--- a/TKIS_queries.xlsx
+++ b/TKIS_queries.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3203" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3193" uniqueCount="746">
   <si>
     <t>TỔNG HỢP CÂU TKIS VÀ GROUND TRUTH</t>
   </si>
@@ -16469,6 +16469,12 @@
     <t/>
   </si>
   <si>
+    <t>K02_V013</t>
+  </si>
+  <si>
+    <t>21549, 21600, 21788, 22064</t>
+  </si>
+  <si>
     <t>Chưa có GT trong nguồn</t>
   </si>
   <si>
@@ -16478,6 +16484,9 @@
     <t>Đoạn video về việc hướng dẫn làm bài tập trắc nghiệm, câu hỏi liên quan đến việc một chất tác dụng với dung dịch màu xanh lam và giải phóng khí hidro. 
 Tổng nguyên tử khối của bốn kim loại đưa ra ở bốn đáp án là 130. Đáp án của câu hỏi này là kim loại có nguyên tử khối là 23.
 Đây là phản ứng của 1 nguyên tố kim loại kiềm (đóng vai trò quan trọng trong phân tử muối ăn thông thường) với CuSO4</t>
+  </si>
+  <si>
+    <t>L25_V084</t>
   </si>
   <si>
     <t>tkis-query-03</t>
@@ -16489,6 +16498,9 @@
 Đây là đoạn clip về chặng 01 vòng đua thành phố Tuyên Quang của Cuộc đua xe đạp Cúp Truyền hình TpHCM</t>
   </si>
   <si>
+    <t>34745, 35021, 35253</t>
+  </si>
+  <si>
     <t>tkis-query-04</t>
   </si>
   <si>
@@ -16498,6 +16510,12 @@
 Đây là đoạn clip về lễ hội Ose Matsuri cầu cho các chuyển đi biển bình an, bội thu tại Nhật</t>
   </si>
   <si>
+    <t>K13_V008</t>
+  </si>
+  <si>
+    <t>23958, 24441</t>
+  </si>
+  <si>
     <t>tkis-query-05</t>
   </si>
   <si>
@@ -16507,6 +16525,9 @@
 Đoạn clip giới thiệu về chè Suối Giàng</t>
   </si>
   <si>
+    <t>K17_V011</t>
+  </si>
+  <si>
     <t>tkis-query-06</t>
   </si>
   <si>
@@ -16515,6 +16536,9 @@
 Một trong các phân cảnh sau đó là nhóm học viên mặc quần áo nông dân cùng áo phao màu đỏ, đang ngồi trên ghe để tham gia hoạt động bắt cá trong trên sông nhỏ</t>
   </si>
   <si>
+    <t>K17_V009</t>
+  </si>
+  <si>
     <t>tkis-query-07</t>
   </si>
   <si>
@@ -16523,6 +16547,12 @@
 Một trong các phân cảnh sau đó là nhóm thiện nguyện đang phát cơm chay 0 đồng trước cổng chùa Chánh Thiên, Bà Rịa.</t>
   </si>
   <si>
+    <t>K13_V015</t>
+  </si>
+  <si>
+    <t>10770, 11241, 11900</t>
+  </si>
+  <si>
     <t>tkis-query-08</t>
   </si>
   <si>
@@ -16531,12 +16561,21 @@
 Có một phân cảnh sau đó phỏng vấn kỹ sư bảo tồn bằng tiếng Pháp. Ông mặc áo đen, đeo kính và đứng trước một hàng rào song sắt màu đen.</t>
   </si>
   <si>
+    <t>K11_V020</t>
+  </si>
+  <si>
     <t>tkis-query-09</t>
   </si>
   <si>
     <t>Đoạn video đưa hình ảnh một vùng nông thôn ở Indonesia người dân có thói quen ngủ trên nguyên liệu thiên nhiên, đặc biệt gây thu hút khách tham quan đến du lịch và trải nghiệm.
 Hình ảnh phỏng vấn người đàn ông là dân địa phương mặc áo ba lỗ màu trằng cùng các em thiếu nhi đang ngồi sinh hoạt trên cát.
 Một trong các phân cảnh sau là hình ảnh một người mặc quần áo màu đen đang nằm trên cát.</t>
+  </si>
+  <si>
+    <t>K14_V025</t>
+  </si>
+  <si>
+    <t>18985, 19148, 19333</t>
   </si>
   <si>
     <t>tkis-query-10</t>
@@ -16548,6 +16587,9 @@
 Đây là đoạn clip về thu thập và tái chế pin (kể cả pin lithium-ion) của chuỗi siêu thị Aldi tại Úc</t>
   </si>
   <si>
+    <t>K19_V011</t>
+  </si>
+  <si>
     <t>tkis-query-12</t>
   </si>
   <si>
@@ -16557,6 +16599,9 @@
 Đây là đoạn clip giới thiệu kỹ thuật làm giảm độ ẩm và chống nóng đặc biệt tại Trường nữ sinh Rajkumari Ratnavati tại Ấn Độ</t>
   </si>
   <si>
+    <t>L22_V024</t>
+  </si>
+  <si>
     <t>tkis-query-13</t>
   </si>
   <si>
@@ -16564,6 +16609,9 @@
 Robot kẹo dẻo có thể chuyển động nhờ hệ thống khí nén bên trong.
 Chiếc bánh có cắm 2 đèn led ăn được. 
 Chiếc bánh với robot và đèn led đều làm từ các nguyên liệu ăn được. Ngay cả pin cũng làm từ Vitamin B2.</t>
+  </si>
+  <si>
+    <t>K15_V003</t>
   </si>
   <si>
     <t>tkis-query-14</t>
@@ -16576,6 +16624,9 @@
 Đây là lễ hội ánh sáng tại Lyon, tổ chức năm 2024</t>
   </si>
   <si>
+    <t>K06_V005</t>
+  </si>
+  <si>
     <t>tkis-query-15</t>
   </si>
   <si>
@@ -16584,6 +16635,9 @@
 Sau đó có hình ảnh các hiện vật trên nền đỏ, ở giữa là 2 ly màu trắng, bên trái là 2 ly lớn trong suốt, bên phải là 1 bình thủy tinh trong suốt. 
 Ở phần đầu đoạn clip có hình ảnh chiếc bình gốm có nắp được trưng bày trong tủ kính, thân bình dáng phình tròn, phủ nền trắng và trang trí bằng họa tiết hoa quả màu hồng đỏ.
 Đây là chương trình triển lãm hàng trăm cổ vật Huế lần đầu được giới thiệu ở Tp.HCM.</t>
+  </si>
+  <si>
+    <t>K05_V009</t>
   </si>
   <si>
     <t>GROUND TRUTH TKIS THEO TỪNG FRAME</t>
@@ -21939,10 +21993,10 @@
         <v>394</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I79" s="6">
         <v>0</v>
@@ -21951,10 +22005,10 @@
         <v>394</v>
       </c>
       <c r="K79" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L79" s="8" t="s">
-        <v>394</v>
+        <v>28</v>
       </c>
     </row>
     <row r="80" ht="72" customHeight="1" spans="1:12">
@@ -21965,22 +22019,22 @@
         <v>390</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>392</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>394</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="H80" s="8" t="s">
-        <v>394</v>
+        <v>400</v>
+      </c>
+      <c r="H80" s="8">
+        <v>21747</v>
       </c>
       <c r="I80" s="6">
         <v>0</v>
@@ -21989,10 +22043,10 @@
         <v>394</v>
       </c>
       <c r="K80" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L80" s="8" t="s">
-        <v>394</v>
+        <v>28</v>
       </c>
     </row>
     <row r="81" ht="72" customHeight="1" spans="1:12">
@@ -22003,22 +22057,22 @@
         <v>390</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>392</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>394</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>394</v>
+        <v>357</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="I81" s="6">
         <v>0</v>
@@ -22027,10 +22081,10 @@
         <v>394</v>
       </c>
       <c r="K81" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L81" s="8" t="s">
-        <v>394</v>
+        <v>28</v>
       </c>
     </row>
     <row r="82" ht="72" customHeight="1" spans="1:12">
@@ -22041,22 +22095,22 @@
         <v>390</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>392</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>394</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="I82" s="6">
         <v>0</v>
@@ -22065,10 +22119,10 @@
         <v>394</v>
       </c>
       <c r="K82" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L82" s="8" t="s">
-        <v>394</v>
+        <v>28</v>
       </c>
     </row>
     <row r="83" ht="72" customHeight="1" spans="1:12">
@@ -22079,22 +22133,22 @@
         <v>390</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>392</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>394</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="H83" s="8" t="s">
-        <v>394</v>
+        <v>410</v>
+      </c>
+      <c r="H83" s="8">
+        <v>11661</v>
       </c>
       <c r="I83" s="6">
         <v>0</v>
@@ -22103,10 +22157,10 @@
         <v>394</v>
       </c>
       <c r="K83" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L83" s="8" t="s">
-        <v>394</v>
+        <v>28</v>
       </c>
     </row>
     <row r="84" ht="72" customHeight="1" spans="1:12">
@@ -22117,22 +22171,22 @@
         <v>390</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>392</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="F84" s="8" t="s">
         <v>394</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="H84" s="8" t="s">
-        <v>394</v>
+        <v>413</v>
+      </c>
+      <c r="H84" s="8">
+        <v>8447</v>
       </c>
       <c r="I84" s="6">
         <v>0</v>
@@ -22141,10 +22195,10 @@
         <v>394</v>
       </c>
       <c r="K84" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L84" s="8" t="s">
-        <v>394</v>
+        <v>28</v>
       </c>
     </row>
     <row r="85" ht="72" customHeight="1" spans="1:12">
@@ -22155,22 +22209,20 @@
         <v>390</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>392</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>407</v>
-      </c>
-      <c r="F85" s="8" t="s">
-        <v>394</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="F85" s="8"/>
       <c r="G85" s="8" t="s">
-        <v>394</v>
+        <v>416</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>394</v>
+        <v>417</v>
       </c>
       <c r="I85" s="6">
         <v>0</v>
@@ -22179,10 +22231,10 @@
         <v>394</v>
       </c>
       <c r="K85" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L85" s="8" t="s">
-        <v>394</v>
+        <v>28</v>
       </c>
     </row>
     <row r="86" ht="72" customHeight="1" spans="1:12">
@@ -22193,22 +22245,22 @@
         <v>390</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>392</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>394</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="H86" s="8" t="s">
-        <v>394</v>
+        <v>420</v>
+      </c>
+      <c r="H86" s="8">
+        <v>30528</v>
       </c>
       <c r="I86" s="6">
         <v>0</v>
@@ -22217,10 +22269,10 @@
         <v>394</v>
       </c>
       <c r="K86" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L86" s="8" t="s">
-        <v>394</v>
+        <v>28</v>
       </c>
     </row>
     <row r="87" ht="72" customHeight="1" spans="1:12">
@@ -22231,22 +22283,22 @@
         <v>390</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>392</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>394</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>394</v>
+        <v>424</v>
       </c>
       <c r="I87" s="6">
         <v>0</v>
@@ -22255,7 +22307,7 @@
         <v>394</v>
       </c>
       <c r="K87" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L87" s="8" t="s">
         <v>394</v>
@@ -22269,22 +22321,22 @@
         <v>390</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>392</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>394</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="H88" s="8" t="s">
-        <v>394</v>
+        <v>427</v>
+      </c>
+      <c r="H88" s="8">
+        <v>21558</v>
       </c>
       <c r="I88" s="6">
         <v>0</v>
@@ -22293,7 +22345,7 @@
         <v>394</v>
       </c>
       <c r="K88" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L88" s="8" t="s">
         <v>394</v>
@@ -22307,22 +22359,22 @@
         <v>390</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="D89" s="6" t="s">
         <v>392</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>394</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="H89" s="8" t="s">
-        <v>394</v>
+        <v>430</v>
+      </c>
+      <c r="H89" s="8">
+        <v>10830</v>
       </c>
       <c r="I89" s="6">
         <v>0</v>
@@ -22331,10 +22383,10 @@
         <v>394</v>
       </c>
       <c r="K89" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L89" s="8" t="s">
-        <v>394</v>
+        <v>28</v>
       </c>
     </row>
     <row r="90" ht="72" customHeight="1" spans="1:12">
@@ -22345,22 +22397,22 @@
         <v>390</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>392</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>394</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="H90" s="8" t="s">
-        <v>394</v>
+        <v>433</v>
+      </c>
+      <c r="H90" s="8">
+        <v>24266</v>
       </c>
       <c r="I90" s="6">
         <v>0</v>
@@ -22369,10 +22421,10 @@
         <v>394</v>
       </c>
       <c r="K90" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L90" s="8" t="s">
-        <v>394</v>
+        <v>28</v>
       </c>
     </row>
     <row r="91" ht="72" customHeight="1" spans="1:12">
@@ -22383,22 +22435,22 @@
         <v>390</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>392</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>419</v>
+        <v>435</v>
       </c>
       <c r="F91" s="8" t="s">
         <v>394</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="H91" s="8" t="s">
-        <v>394</v>
+        <v>436</v>
+      </c>
+      <c r="H91" s="8">
+        <v>22140</v>
       </c>
       <c r="I91" s="6">
         <v>0</v>
@@ -22407,10 +22459,10 @@
         <v>394</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L91" s="8" t="s">
-        <v>394</v>
+        <v>28</v>
       </c>
     </row>
     <row r="92" ht="72" customHeight="1" spans="1:12">
@@ -22421,22 +22473,22 @@
         <v>390</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>392</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>394</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="H92" s="8" t="s">
-        <v>394</v>
+        <v>439</v>
+      </c>
+      <c r="H92" s="8">
+        <v>6392</v>
       </c>
       <c r="I92" s="6">
         <v>0</v>
@@ -22445,10 +22497,10 @@
         <v>394</v>
       </c>
       <c r="K92" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L92" s="8" t="s">
-        <v>394</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -22493,7 +22545,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:8">
       <c r="A1" s="2" t="s">
-        <v>422</v>
+        <v>440</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -22543,7 +22595,7 @@
         <v>24</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>26</v>
@@ -22569,7 +22621,7 @@
         <v>24</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>26</v>
@@ -22595,7 +22647,7 @@
         <v>32</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>26</v>
@@ -22621,7 +22673,7 @@
         <v>32</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>26</v>
@@ -22647,7 +22699,7 @@
         <v>32</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>26</v>
@@ -22673,7 +22725,7 @@
         <v>32</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>26</v>
@@ -22699,7 +22751,7 @@
         <v>37</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>26</v>
@@ -22725,7 +22777,7 @@
         <v>37</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>26</v>
@@ -22751,7 +22803,7 @@
         <v>42</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>26</v>
@@ -22777,7 +22829,7 @@
         <v>42</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>26</v>
@@ -22803,7 +22855,7 @@
         <v>42</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>26</v>
@@ -22829,7 +22881,7 @@
         <v>47</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>434</v>
+        <v>452</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>26</v>
@@ -22855,7 +22907,7 @@
         <v>47</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>26</v>
@@ -22881,7 +22933,7 @@
         <v>52</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>436</v>
+        <v>454</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>26</v>
@@ -22907,7 +22959,7 @@
         <v>52</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>26</v>
@@ -22933,7 +22985,7 @@
         <v>56</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>26</v>
@@ -22959,7 +23011,7 @@
         <v>56</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>26</v>
@@ -22985,7 +23037,7 @@
         <v>61</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>26</v>
@@ -23011,7 +23063,7 @@
         <v>66</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>26</v>
@@ -23037,7 +23089,7 @@
         <v>66</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>26</v>
@@ -23063,7 +23115,7 @@
         <v>66</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>26</v>
@@ -23080,7 +23132,7 @@
         <v>19</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>21</v>
@@ -23089,7 +23141,7 @@
         <v>70</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>26</v>
@@ -23098,7 +23150,7 @@
         <v>27</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1" spans="1:8">
@@ -23106,7 +23158,7 @@
         <v>19</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>21</v>
@@ -23115,7 +23167,7 @@
         <v>70</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>26</v>
@@ -23124,7 +23176,7 @@
         <v>27</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
     </row>
     <row r="27" ht="42" customHeight="1" spans="1:8">
@@ -23132,7 +23184,7 @@
         <v>19</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>21</v>
@@ -23141,7 +23193,7 @@
         <v>70</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>26</v>
@@ -23150,7 +23202,7 @@
         <v>27</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
     </row>
     <row r="28" ht="42" customHeight="1" spans="1:8">
@@ -23158,7 +23210,7 @@
         <v>19</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>21</v>
@@ -23167,7 +23219,7 @@
         <v>70</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>26</v>
@@ -23176,7 +23228,7 @@
         <v>27</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
     </row>
     <row r="29" ht="42" customHeight="1" spans="1:8">
@@ -23184,7 +23236,7 @@
         <v>19</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>21</v>
@@ -23193,7 +23245,7 @@
         <v>70</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>26</v>
@@ -23202,7 +23254,7 @@
         <v>27</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
     </row>
     <row r="30" ht="42" customHeight="1" spans="1:8">
@@ -23219,7 +23271,7 @@
         <v>76</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>26</v>
@@ -23245,7 +23297,7 @@
         <v>76</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>452</v>
+        <v>470</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>26</v>
@@ -23271,7 +23323,7 @@
         <v>76</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>26</v>
@@ -23297,7 +23349,7 @@
         <v>76</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>454</v>
+        <v>472</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>26</v>
@@ -23323,7 +23375,7 @@
         <v>81</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>26</v>
@@ -23349,7 +23401,7 @@
         <v>81</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>456</v>
+        <v>474</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>26</v>
@@ -23447,7 +23499,7 @@
         <v>103</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>26</v>
@@ -23473,7 +23525,7 @@
         <v>103</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>26</v>
@@ -23499,7 +23551,7 @@
         <v>103</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>26</v>
@@ -23525,7 +23577,7 @@
         <v>103</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>460</v>
+        <v>478</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>26</v>
@@ -23603,7 +23655,7 @@
         <v>120</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>26</v>
@@ -23629,7 +23681,7 @@
         <v>120</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>26</v>
@@ -23655,7 +23707,7 @@
         <v>120</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>26</v>
@@ -23681,7 +23733,7 @@
         <v>125</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>26</v>
@@ -23707,7 +23759,7 @@
         <v>125</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>26</v>
@@ -23733,7 +23785,7 @@
         <v>125</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>26</v>
@@ -23759,7 +23811,7 @@
         <v>125</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>26</v>
@@ -23785,7 +23837,7 @@
         <v>125</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>468</v>
+        <v>486</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>26</v>
@@ -23811,7 +23863,7 @@
         <v>125</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>26</v>
@@ -23837,7 +23889,7 @@
         <v>130</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>470</v>
+        <v>488</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>26</v>
@@ -23863,7 +23915,7 @@
         <v>130</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>471</v>
+        <v>489</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>26</v>
@@ -23889,7 +23941,7 @@
         <v>130</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>472</v>
+        <v>490</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>26</v>
@@ -23915,7 +23967,7 @@
         <v>134</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>26</v>
@@ -23941,7 +23993,7 @@
         <v>134</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>26</v>
@@ -23967,7 +24019,7 @@
         <v>134</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>26</v>
@@ -23993,7 +24045,7 @@
         <v>134</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>476</v>
+        <v>494</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>26</v>
@@ -24019,7 +24071,7 @@
         <v>134</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>477</v>
+        <v>495</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>26</v>
@@ -24045,7 +24097,7 @@
         <v>139</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>26</v>
@@ -24071,7 +24123,7 @@
         <v>139</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>26</v>
@@ -24097,7 +24149,7 @@
         <v>139</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>480</v>
+        <v>498</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>26</v>
@@ -24123,7 +24175,7 @@
         <v>139</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>481</v>
+        <v>499</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>26</v>
@@ -24149,7 +24201,7 @@
         <v>144</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>26</v>
@@ -24175,7 +24227,7 @@
         <v>144</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>483</v>
+        <v>501</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>26</v>
@@ -24201,7 +24253,7 @@
         <v>144</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>484</v>
+        <v>502</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>26</v>
@@ -24227,7 +24279,7 @@
         <v>149</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>485</v>
+        <v>503</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>26</v>
@@ -24253,7 +24305,7 @@
         <v>149</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>26</v>
@@ -24279,7 +24331,7 @@
         <v>149</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>487</v>
+        <v>505</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>26</v>
@@ -24305,7 +24357,7 @@
         <v>149</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>26</v>
@@ -24331,7 +24383,7 @@
         <v>149</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>26</v>
@@ -24357,7 +24409,7 @@
         <v>149</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>26</v>
@@ -24383,7 +24435,7 @@
         <v>154</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>491</v>
+        <v>509</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>26</v>
@@ -24409,7 +24461,7 @@
         <v>154</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>492</v>
+        <v>510</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>26</v>
@@ -24435,7 +24487,7 @@
         <v>160</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>26</v>
@@ -24461,7 +24513,7 @@
         <v>160</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>26</v>
@@ -24487,7 +24539,7 @@
         <v>160</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>26</v>
@@ -24513,7 +24565,7 @@
         <v>160</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>26</v>
@@ -24539,7 +24591,7 @@
         <v>160</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>26</v>
@@ -24565,7 +24617,7 @@
         <v>165</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>498</v>
+        <v>516</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>26</v>
@@ -24574,7 +24626,7 @@
         <v>27</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
     </row>
     <row r="83" ht="42" customHeight="1" spans="1:8">
@@ -24588,10 +24640,10 @@
         <v>21</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>500</v>
+        <v>518</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>501</v>
+        <v>519</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>26</v>
@@ -24600,7 +24652,7 @@
         <v>27</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
     </row>
     <row r="84" ht="42" customHeight="1" spans="1:8">
@@ -24617,7 +24669,7 @@
         <v>165</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>502</v>
+        <v>520</v>
       </c>
       <c r="F84" s="4" t="s">
         <v>26</v>
@@ -24626,7 +24678,7 @@
         <v>27</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
     </row>
     <row r="85" ht="42" customHeight="1" spans="1:8">
@@ -24640,10 +24692,10 @@
         <v>21</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>500</v>
+        <v>518</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>503</v>
+        <v>521</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>26</v>
@@ -24652,7 +24704,7 @@
         <v>27</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
     </row>
     <row r="86" ht="42" customHeight="1" spans="1:8">
@@ -24666,10 +24718,10 @@
         <v>21</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>500</v>
+        <v>518</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>504</v>
+        <v>522</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>26</v>
@@ -24678,7 +24730,7 @@
         <v>27</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
     </row>
     <row r="87" ht="42" customHeight="1" spans="1:8">
@@ -24695,7 +24747,7 @@
         <v>170</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>505</v>
+        <v>523</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>26</v>
@@ -24704,7 +24756,7 @@
         <v>27</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>506</v>
+        <v>524</v>
       </c>
     </row>
     <row r="88" ht="42" customHeight="1" spans="1:8">
@@ -24721,7 +24773,7 @@
         <v>170</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>26</v>
@@ -24730,7 +24782,7 @@
         <v>27</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>506</v>
+        <v>524</v>
       </c>
     </row>
     <row r="89" ht="42" customHeight="1" spans="1:8">
@@ -24747,7 +24799,7 @@
         <v>170</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>508</v>
+        <v>526</v>
       </c>
       <c r="F89" s="4" t="s">
         <v>26</v>
@@ -24756,7 +24808,7 @@
         <v>27</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>506</v>
+        <v>524</v>
       </c>
     </row>
     <row r="90" ht="42" customHeight="1" spans="1:8">
@@ -24773,7 +24825,7 @@
         <v>170</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>509</v>
+        <v>527</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>26</v>
@@ -24782,7 +24834,7 @@
         <v>27</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>506</v>
+        <v>524</v>
       </c>
     </row>
     <row r="91" ht="42" customHeight="1" spans="1:8">
@@ -24799,7 +24851,7 @@
         <v>170</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>510</v>
+        <v>528</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>26</v>
@@ -24808,7 +24860,7 @@
         <v>27</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>506</v>
+        <v>524</v>
       </c>
     </row>
     <row r="92" ht="42" customHeight="1" spans="1:8">
@@ -24834,7 +24886,7 @@
         <v>27</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>511</v>
+        <v>529</v>
       </c>
     </row>
     <row r="93" ht="42" customHeight="1" spans="1:8">
@@ -24851,7 +24903,7 @@
         <v>182</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>512</v>
+        <v>530</v>
       </c>
       <c r="F93" s="4" t="s">
         <v>88</v>
@@ -24860,7 +24912,7 @@
         <v>184</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>513</v>
+        <v>531</v>
       </c>
     </row>
     <row r="94" ht="42" customHeight="1" spans="1:8">
@@ -24877,7 +24929,7 @@
         <v>182</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>88</v>
@@ -24886,7 +24938,7 @@
         <v>184</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>513</v>
+        <v>531</v>
       </c>
     </row>
     <row r="95" ht="42" customHeight="1" spans="1:8">
@@ -24903,7 +24955,7 @@
         <v>182</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>515</v>
+        <v>533</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>88</v>
@@ -24912,7 +24964,7 @@
         <v>184</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>513</v>
+        <v>531</v>
       </c>
     </row>
     <row r="96" ht="42" customHeight="1" spans="1:8">
@@ -24934,7 +24986,7 @@
         <v>188</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
     </row>
     <row r="97" ht="42" customHeight="1" spans="1:8">
@@ -24951,7 +25003,7 @@
         <v>192</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>517</v>
+        <v>535</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>88</v>
@@ -24960,7 +25012,7 @@
         <v>184</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>518</v>
+        <v>536</v>
       </c>
     </row>
     <row r="98" ht="42" customHeight="1" spans="1:8">
@@ -24977,7 +25029,7 @@
         <v>192</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="F98" s="4" t="s">
         <v>88</v>
@@ -24986,7 +25038,7 @@
         <v>184</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>518</v>
+        <v>536</v>
       </c>
     </row>
     <row r="99" ht="42" customHeight="1" spans="1:8">
@@ -25003,7 +25055,7 @@
         <v>196</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>520</v>
+        <v>538</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>26</v>
@@ -25012,7 +25064,7 @@
         <v>27</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
     </row>
     <row r="100" ht="42" customHeight="1" spans="1:8">
@@ -25029,7 +25081,7 @@
         <v>196</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>26</v>
@@ -25038,7 +25090,7 @@
         <v>27</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
     </row>
     <row r="101" ht="42" customHeight="1" spans="1:8">
@@ -25055,7 +25107,7 @@
         <v>196</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>523</v>
+        <v>541</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>26</v>
@@ -25064,7 +25116,7 @@
         <v>27</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
     </row>
     <row r="102" ht="42" customHeight="1" spans="1:8">
@@ -25081,7 +25133,7 @@
         <v>201</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>524</v>
+        <v>542</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>88</v>
@@ -25090,7 +25142,7 @@
         <v>184</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>525</v>
+        <v>543</v>
       </c>
     </row>
     <row r="103" ht="42" customHeight="1" spans="1:8">
@@ -25107,7 +25159,7 @@
         <v>201</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>526</v>
+        <v>544</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>88</v>
@@ -25116,7 +25168,7 @@
         <v>184</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>525</v>
+        <v>543</v>
       </c>
     </row>
     <row r="104" ht="42" customHeight="1" spans="1:8">
@@ -25133,7 +25185,7 @@
         <v>201</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>88</v>
@@ -25142,7 +25194,7 @@
         <v>184</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>525</v>
+        <v>543</v>
       </c>
     </row>
     <row r="105" ht="42" customHeight="1" spans="1:8">
@@ -25159,7 +25211,7 @@
         <v>206</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>528</v>
+        <v>546</v>
       </c>
       <c r="F105" s="4" t="s">
         <v>26</v>
@@ -25168,7 +25220,7 @@
         <v>27</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
     </row>
     <row r="106" ht="42" customHeight="1" spans="1:8">
@@ -25185,7 +25237,7 @@
         <v>206</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>530</v>
+        <v>548</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>26</v>
@@ -25194,7 +25246,7 @@
         <v>27</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
     </row>
     <row r="107" ht="42" customHeight="1" spans="1:8">
@@ -25211,7 +25263,7 @@
         <v>206</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>531</v>
+        <v>549</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>26</v>
@@ -25220,7 +25272,7 @@
         <v>27</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
     </row>
     <row r="108" ht="42" customHeight="1" spans="1:8">
@@ -25237,7 +25289,7 @@
         <v>206</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>532</v>
+        <v>550</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>26</v>
@@ -25246,7 +25298,7 @@
         <v>27</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
     </row>
     <row r="109" ht="42" customHeight="1" spans="1:8">
@@ -25263,7 +25315,7 @@
         <v>206</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>26</v>
@@ -25272,7 +25324,7 @@
         <v>27</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
     </row>
     <row r="110" ht="42" customHeight="1" spans="1:8">
@@ -25289,7 +25341,7 @@
         <v>206</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>26</v>
@@ -25298,7 +25350,7 @@
         <v>27</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
     </row>
     <row r="111" ht="42" customHeight="1" spans="1:8">
@@ -25315,7 +25367,7 @@
         <v>206</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>535</v>
+        <v>553</v>
       </c>
       <c r="F111" s="4" t="s">
         <v>26</v>
@@ -25324,7 +25376,7 @@
         <v>27</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
     </row>
     <row r="112" ht="42" customHeight="1" spans="1:8">
@@ -25341,7 +25393,7 @@
         <v>206</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>536</v>
+        <v>554</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>26</v>
@@ -25350,7 +25402,7 @@
         <v>27</v>
       </c>
       <c r="H112" s="5" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
     </row>
     <row r="113" ht="42" customHeight="1" spans="1:8">
@@ -25367,7 +25419,7 @@
         <v>206</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>26</v>
@@ -25376,7 +25428,7 @@
         <v>27</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
     </row>
     <row r="114" ht="42" customHeight="1" spans="1:8">
@@ -25393,7 +25445,7 @@
         <v>206</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="F114" s="4" t="s">
         <v>26</v>
@@ -25402,7 +25454,7 @@
         <v>27</v>
       </c>
       <c r="H114" s="5" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
     </row>
     <row r="115" ht="42" customHeight="1" spans="1:8">
@@ -25419,7 +25471,7 @@
         <v>206</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>539</v>
+        <v>557</v>
       </c>
       <c r="F115" s="4" t="s">
         <v>26</v>
@@ -25428,7 +25480,7 @@
         <v>27</v>
       </c>
       <c r="H115" s="5" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
     </row>
     <row r="116" ht="42" customHeight="1" spans="1:8">
@@ -25445,7 +25497,7 @@
         <v>206</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="F116" s="4" t="s">
         <v>26</v>
@@ -25454,7 +25506,7 @@
         <v>27</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
     </row>
     <row r="117" ht="42" customHeight="1" spans="1:8">
@@ -25471,7 +25523,7 @@
         <v>206</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>26</v>
@@ -25480,7 +25532,7 @@
         <v>27</v>
       </c>
       <c r="H117" s="5" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
     </row>
     <row r="118" ht="42" customHeight="1" spans="1:8">
@@ -25497,7 +25549,7 @@
         <v>206</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>542</v>
+        <v>560</v>
       </c>
       <c r="F118" s="4" t="s">
         <v>26</v>
@@ -25506,7 +25558,7 @@
         <v>27</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
     </row>
     <row r="119" ht="42" customHeight="1" spans="1:8">
@@ -25523,7 +25575,7 @@
         <v>206</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="F119" s="4" t="s">
         <v>26</v>
@@ -25532,7 +25584,7 @@
         <v>27</v>
       </c>
       <c r="H119" s="5" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
     </row>
     <row r="120" ht="42" customHeight="1" spans="1:8">
@@ -25549,7 +25601,7 @@
         <v>206</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>544</v>
+        <v>562</v>
       </c>
       <c r="F120" s="4" t="s">
         <v>26</v>
@@ -25558,7 +25610,7 @@
         <v>27</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
     </row>
     <row r="121" ht="42" customHeight="1" spans="1:8">
@@ -25575,7 +25627,7 @@
         <v>206</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>545</v>
+        <v>563</v>
       </c>
       <c r="F121" s="4" t="s">
         <v>26</v>
@@ -25584,7 +25636,7 @@
         <v>27</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
     </row>
     <row r="122" ht="42" customHeight="1" spans="1:8">
@@ -25601,7 +25653,7 @@
         <v>206</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>546</v>
+        <v>564</v>
       </c>
       <c r="F122" s="4" t="s">
         <v>26</v>
@@ -25610,7 +25662,7 @@
         <v>27</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
     </row>
     <row r="123" ht="42" customHeight="1" spans="1:8">
@@ -25627,7 +25679,7 @@
         <v>211</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>547</v>
+        <v>565</v>
       </c>
       <c r="F123" s="4" t="s">
         <v>88</v>
@@ -25636,7 +25688,7 @@
         <v>184</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>548</v>
+        <v>566</v>
       </c>
     </row>
     <row r="124" ht="42" customHeight="1" spans="1:8">
@@ -25653,7 +25705,7 @@
         <v>211</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>549</v>
+        <v>567</v>
       </c>
       <c r="F124" s="4" t="s">
         <v>88</v>
@@ -25662,7 +25714,7 @@
         <v>184</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>548</v>
+        <v>566</v>
       </c>
     </row>
     <row r="125" ht="42" customHeight="1" spans="1:8">
@@ -25679,7 +25731,7 @@
         <v>216</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>550</v>
+        <v>568</v>
       </c>
       <c r="F125" s="4" t="s">
         <v>26</v>
@@ -25688,7 +25740,7 @@
         <v>27</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>551</v>
+        <v>569</v>
       </c>
     </row>
     <row r="126" ht="42" customHeight="1" spans="1:8">
@@ -25705,7 +25757,7 @@
         <v>216</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>552</v>
+        <v>570</v>
       </c>
       <c r="F126" s="4" t="s">
         <v>26</v>
@@ -25714,7 +25766,7 @@
         <v>27</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>551</v>
+        <v>569</v>
       </c>
     </row>
     <row r="127" ht="42" customHeight="1" spans="1:8">
@@ -25731,7 +25783,7 @@
         <v>216</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>508</v>
+        <v>526</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>26</v>
@@ -25740,7 +25792,7 @@
         <v>27</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>551</v>
+        <v>569</v>
       </c>
     </row>
     <row r="128" ht="42" customHeight="1" spans="1:8">
@@ -25757,7 +25809,7 @@
         <v>216</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>510</v>
+        <v>528</v>
       </c>
       <c r="F128" s="4" t="s">
         <v>26</v>
@@ -25766,7 +25818,7 @@
         <v>27</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>551</v>
+        <v>569</v>
       </c>
     </row>
     <row r="129" ht="42" customHeight="1" spans="1:8">
@@ -25783,7 +25835,7 @@
         <v>216</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>553</v>
+        <v>571</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>26</v>
@@ -25792,7 +25844,7 @@
         <v>27</v>
       </c>
       <c r="H129" s="5" t="s">
-        <v>551</v>
+        <v>569</v>
       </c>
     </row>
     <row r="130" ht="42" customHeight="1" spans="1:8">
@@ -25809,7 +25861,7 @@
         <v>216</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>554</v>
+        <v>572</v>
       </c>
       <c r="F130" s="4" t="s">
         <v>26</v>
@@ -25818,7 +25870,7 @@
         <v>27</v>
       </c>
       <c r="H130" s="5" t="s">
-        <v>551</v>
+        <v>569</v>
       </c>
     </row>
     <row r="131" ht="42" customHeight="1" spans="1:8">
@@ -25835,7 +25887,7 @@
         <v>216</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>555</v>
+        <v>573</v>
       </c>
       <c r="F131" s="4" t="s">
         <v>26</v>
@@ -25844,7 +25896,7 @@
         <v>27</v>
       </c>
       <c r="H131" s="5" t="s">
-        <v>551</v>
+        <v>569</v>
       </c>
     </row>
     <row r="132" ht="42" customHeight="1" spans="1:8">
@@ -25861,7 +25913,7 @@
         <v>216</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>556</v>
+        <v>574</v>
       </c>
       <c r="F132" s="4" t="s">
         <v>26</v>
@@ -25870,7 +25922,7 @@
         <v>27</v>
       </c>
       <c r="H132" s="5" t="s">
-        <v>551</v>
+        <v>569</v>
       </c>
     </row>
     <row r="133" ht="42" customHeight="1" spans="1:8">
@@ -25887,7 +25939,7 @@
         <v>236</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>557</v>
+        <v>575</v>
       </c>
       <c r="F133" s="4" t="s">
         <v>88</v>
@@ -25896,7 +25948,7 @@
         <v>184</v>
       </c>
       <c r="H133" s="5" t="s">
-        <v>558</v>
+        <v>576</v>
       </c>
     </row>
     <row r="134" ht="42" customHeight="1" spans="1:8">
@@ -25913,7 +25965,7 @@
         <v>236</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>559</v>
+        <v>577</v>
       </c>
       <c r="F134" s="4" t="s">
         <v>88</v>
@@ -25922,7 +25974,7 @@
         <v>184</v>
       </c>
       <c r="H134" s="5" t="s">
-        <v>558</v>
+        <v>576</v>
       </c>
     </row>
     <row r="135" ht="42" customHeight="1" spans="1:8">
@@ -25939,7 +25991,7 @@
         <v>236</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>560</v>
+        <v>578</v>
       </c>
       <c r="F135" s="4" t="s">
         <v>88</v>
@@ -25948,7 +26000,7 @@
         <v>184</v>
       </c>
       <c r="H135" s="5" t="s">
-        <v>558</v>
+        <v>576</v>
       </c>
     </row>
     <row r="136" ht="42" customHeight="1" spans="1:8">
@@ -25965,7 +26017,7 @@
         <v>236</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>561</v>
+        <v>579</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>88</v>
@@ -25974,7 +26026,7 @@
         <v>184</v>
       </c>
       <c r="H136" s="5" t="s">
-        <v>558</v>
+        <v>576</v>
       </c>
     </row>
     <row r="137" ht="42" customHeight="1" spans="1:8">
@@ -25991,7 +26043,7 @@
         <v>226</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>562</v>
+        <v>580</v>
       </c>
       <c r="F137" s="4" t="s">
         <v>88</v>
@@ -26000,7 +26052,7 @@
         <v>184</v>
       </c>
       <c r="H137" s="5" t="s">
-        <v>563</v>
+        <v>581</v>
       </c>
     </row>
     <row r="138" ht="42" customHeight="1" spans="1:8">
@@ -26017,7 +26069,7 @@
         <v>226</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>564</v>
+        <v>582</v>
       </c>
       <c r="F138" s="4" t="s">
         <v>88</v>
@@ -26026,7 +26078,7 @@
         <v>184</v>
       </c>
       <c r="H138" s="5" t="s">
-        <v>563</v>
+        <v>581</v>
       </c>
     </row>
     <row r="139" ht="42" customHeight="1" spans="1:8">
@@ -26043,7 +26095,7 @@
         <v>226</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>565</v>
+        <v>583</v>
       </c>
       <c r="F139" s="4" t="s">
         <v>88</v>
@@ -26052,7 +26104,7 @@
         <v>184</v>
       </c>
       <c r="H139" s="5" t="s">
-        <v>563</v>
+        <v>581</v>
       </c>
     </row>
     <row r="140" ht="42" customHeight="1" spans="1:8">
@@ -26069,7 +26121,7 @@
         <v>232</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>566</v>
+        <v>584</v>
       </c>
       <c r="F140" s="4" t="s">
         <v>88</v>
@@ -26078,7 +26130,7 @@
         <v>184</v>
       </c>
       <c r="H140" s="5" t="s">
-        <v>567</v>
+        <v>585</v>
       </c>
     </row>
     <row r="141" ht="42" customHeight="1" spans="1:8">
@@ -26095,7 +26147,7 @@
         <v>232</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>568</v>
+        <v>586</v>
       </c>
       <c r="F141" s="4" t="s">
         <v>88</v>
@@ -26104,7 +26156,7 @@
         <v>184</v>
       </c>
       <c r="H141" s="5" t="s">
-        <v>567</v>
+        <v>585</v>
       </c>
     </row>
     <row r="142" ht="42" customHeight="1" spans="1:8">
@@ -26121,7 +26173,7 @@
         <v>232</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>569</v>
+        <v>587</v>
       </c>
       <c r="F142" s="4" t="s">
         <v>88</v>
@@ -26130,7 +26182,7 @@
         <v>184</v>
       </c>
       <c r="H142" s="5" t="s">
-        <v>567</v>
+        <v>585</v>
       </c>
     </row>
     <row r="143" ht="42" customHeight="1" spans="1:8">
@@ -26147,7 +26199,7 @@
         <v>232</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>570</v>
+        <v>588</v>
       </c>
       <c r="F143" s="4" t="s">
         <v>88</v>
@@ -26156,7 +26208,7 @@
         <v>184</v>
       </c>
       <c r="H143" s="5" t="s">
-        <v>567</v>
+        <v>585</v>
       </c>
     </row>
     <row r="144" ht="42" customHeight="1" spans="1:8">
@@ -26173,7 +26225,7 @@
         <v>232</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="F144" s="4" t="s">
         <v>88</v>
@@ -26182,7 +26234,7 @@
         <v>184</v>
       </c>
       <c r="H144" s="5" t="s">
-        <v>567</v>
+        <v>585</v>
       </c>
     </row>
     <row r="145" ht="42" customHeight="1" spans="1:8">
@@ -26199,7 +26251,7 @@
         <v>232</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>571</v>
+        <v>589</v>
       </c>
       <c r="F145" s="4" t="s">
         <v>88</v>
@@ -26208,7 +26260,7 @@
         <v>184</v>
       </c>
       <c r="H145" s="5" t="s">
-        <v>567</v>
+        <v>585</v>
       </c>
     </row>
     <row r="146" ht="42" customHeight="1" spans="1:8">
@@ -26225,7 +26277,7 @@
         <v>236</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>557</v>
+        <v>575</v>
       </c>
       <c r="F146" s="4" t="s">
         <v>88</v>
@@ -26234,7 +26286,7 @@
         <v>184</v>
       </c>
       <c r="H146" s="5" t="s">
-        <v>572</v>
+        <v>590</v>
       </c>
     </row>
     <row r="147" ht="42" customHeight="1" spans="1:8">
@@ -26251,7 +26303,7 @@
         <v>236</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>559</v>
+        <v>577</v>
       </c>
       <c r="F147" s="4" t="s">
         <v>88</v>
@@ -26260,7 +26312,7 @@
         <v>184</v>
       </c>
       <c r="H147" s="5" t="s">
-        <v>572</v>
+        <v>590</v>
       </c>
     </row>
     <row r="148" ht="42" customHeight="1" spans="1:8">
@@ -26277,7 +26329,7 @@
         <v>236</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>560</v>
+        <v>578</v>
       </c>
       <c r="F148" s="4" t="s">
         <v>88</v>
@@ -26286,7 +26338,7 @@
         <v>184</v>
       </c>
       <c r="H148" s="5" t="s">
-        <v>572</v>
+        <v>590</v>
       </c>
     </row>
     <row r="149" ht="42" customHeight="1" spans="1:8">
@@ -26303,7 +26355,7 @@
         <v>236</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>561</v>
+        <v>579</v>
       </c>
       <c r="F149" s="4" t="s">
         <v>88</v>
@@ -26312,7 +26364,7 @@
         <v>184</v>
       </c>
       <c r="H149" s="5" t="s">
-        <v>572</v>
+        <v>590</v>
       </c>
     </row>
     <row r="150" ht="42" customHeight="1" spans="1:8">
@@ -26329,7 +26381,7 @@
         <v>242</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="F150" s="4" t="s">
         <v>26</v>
@@ -26338,7 +26390,7 @@
         <v>27</v>
       </c>
       <c r="H150" s="5" t="s">
-        <v>574</v>
+        <v>592</v>
       </c>
     </row>
     <row r="151" ht="42" customHeight="1" spans="1:8">
@@ -26355,7 +26407,7 @@
         <v>242</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>575</v>
+        <v>593</v>
       </c>
       <c r="F151" s="4" t="s">
         <v>26</v>
@@ -26364,7 +26416,7 @@
         <v>27</v>
       </c>
       <c r="H151" s="5" t="s">
-        <v>574</v>
+        <v>592</v>
       </c>
     </row>
     <row r="152" ht="42" customHeight="1" spans="1:8">
@@ -26381,7 +26433,7 @@
         <v>242</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>576</v>
+        <v>594</v>
       </c>
       <c r="F152" s="4" t="s">
         <v>26</v>
@@ -26390,7 +26442,7 @@
         <v>27</v>
       </c>
       <c r="H152" s="5" t="s">
-        <v>574</v>
+        <v>592</v>
       </c>
     </row>
     <row r="153" ht="42" customHeight="1" spans="1:8">
@@ -26407,7 +26459,7 @@
         <v>242</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>577</v>
+        <v>595</v>
       </c>
       <c r="F153" s="4" t="s">
         <v>26</v>
@@ -26416,7 +26468,7 @@
         <v>27</v>
       </c>
       <c r="H153" s="5" t="s">
-        <v>574</v>
+        <v>592</v>
       </c>
     </row>
     <row r="154" ht="42" customHeight="1" spans="1:8">
@@ -26433,7 +26485,7 @@
         <v>242</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>578</v>
+        <v>596</v>
       </c>
       <c r="F154" s="4" t="s">
         <v>26</v>
@@ -26442,7 +26494,7 @@
         <v>27</v>
       </c>
       <c r="H154" s="5" t="s">
-        <v>574</v>
+        <v>592</v>
       </c>
     </row>
     <row r="155" ht="42" customHeight="1" spans="1:8">
@@ -26459,7 +26511,7 @@
         <v>248</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>579</v>
+        <v>597</v>
       </c>
       <c r="F155" s="4" t="s">
         <v>26</v>
@@ -26468,7 +26520,7 @@
         <v>27</v>
       </c>
       <c r="H155" s="5" t="s">
-        <v>580</v>
+        <v>598</v>
       </c>
     </row>
     <row r="156" ht="42" customHeight="1" spans="1:8">
@@ -26485,7 +26537,7 @@
         <v>248</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>581</v>
+        <v>599</v>
       </c>
       <c r="F156" s="4" t="s">
         <v>26</v>
@@ -26494,7 +26546,7 @@
         <v>27</v>
       </c>
       <c r="H156" s="5" t="s">
-        <v>580</v>
+        <v>598</v>
       </c>
     </row>
     <row r="157" ht="42" customHeight="1" spans="1:8">
@@ -26511,7 +26563,7 @@
         <v>248</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>582</v>
+        <v>600</v>
       </c>
       <c r="F157" s="4" t="s">
         <v>26</v>
@@ -26520,7 +26572,7 @@
         <v>27</v>
       </c>
       <c r="H157" s="5" t="s">
-        <v>580</v>
+        <v>598</v>
       </c>
     </row>
     <row r="158" ht="42" customHeight="1" spans="1:8">
@@ -26537,7 +26589,7 @@
         <v>248</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>583</v>
+        <v>601</v>
       </c>
       <c r="F158" s="4" t="s">
         <v>26</v>
@@ -26546,7 +26598,7 @@
         <v>27</v>
       </c>
       <c r="H158" s="5" t="s">
-        <v>580</v>
+        <v>598</v>
       </c>
     </row>
     <row r="159" ht="42" customHeight="1" spans="1:8">
@@ -26563,7 +26615,7 @@
         <v>248</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>584</v>
+        <v>602</v>
       </c>
       <c r="F159" s="4" t="s">
         <v>26</v>
@@ -26572,7 +26624,7 @@
         <v>27</v>
       </c>
       <c r="H159" s="5" t="s">
-        <v>580</v>
+        <v>598</v>
       </c>
     </row>
     <row r="160" ht="42" customHeight="1" spans="1:8">
@@ -26589,7 +26641,7 @@
         <v>248</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>585</v>
+        <v>603</v>
       </c>
       <c r="F160" s="4" t="s">
         <v>26</v>
@@ -26598,7 +26650,7 @@
         <v>27</v>
       </c>
       <c r="H160" s="5" t="s">
-        <v>580</v>
+        <v>598</v>
       </c>
     </row>
     <row r="161" ht="42" customHeight="1" spans="1:8">
@@ -26615,7 +26667,7 @@
         <v>248</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="F161" s="4" t="s">
         <v>26</v>
@@ -26624,7 +26676,7 @@
         <v>27</v>
       </c>
       <c r="H161" s="5" t="s">
-        <v>580</v>
+        <v>598</v>
       </c>
     </row>
     <row r="162" ht="42" customHeight="1" spans="1:8">
@@ -26641,7 +26693,7 @@
         <v>248</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>587</v>
+        <v>605</v>
       </c>
       <c r="F162" s="4" t="s">
         <v>26</v>
@@ -26650,7 +26702,7 @@
         <v>27</v>
       </c>
       <c r="H162" s="5" t="s">
-        <v>580</v>
+        <v>598</v>
       </c>
     </row>
     <row r="163" ht="42" customHeight="1" spans="1:8">
@@ -26667,7 +26719,7 @@
         <v>248</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>588</v>
+        <v>606</v>
       </c>
       <c r="F163" s="4" t="s">
         <v>26</v>
@@ -26676,7 +26728,7 @@
         <v>27</v>
       </c>
       <c r="H163" s="5" t="s">
-        <v>580</v>
+        <v>598</v>
       </c>
     </row>
     <row r="164" ht="42" customHeight="1" spans="1:8">
@@ -26693,7 +26745,7 @@
         <v>248</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>589</v>
+        <v>607</v>
       </c>
       <c r="F164" s="4" t="s">
         <v>26</v>
@@ -26702,7 +26754,7 @@
         <v>27</v>
       </c>
       <c r="H164" s="5" t="s">
-        <v>580</v>
+        <v>598</v>
       </c>
     </row>
     <row r="165" ht="42" customHeight="1" spans="1:8">
@@ -26719,7 +26771,7 @@
         <v>254</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>590</v>
+        <v>608</v>
       </c>
       <c r="F165" s="4" t="s">
         <v>26</v>
@@ -26728,7 +26780,7 @@
         <v>27</v>
       </c>
       <c r="H165" s="5" t="s">
-        <v>591</v>
+        <v>609</v>
       </c>
     </row>
     <row r="166" ht="42" customHeight="1" spans="1:8">
@@ -26745,7 +26797,7 @@
         <v>254</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>592</v>
+        <v>610</v>
       </c>
       <c r="F166" s="4" t="s">
         <v>26</v>
@@ -26754,7 +26806,7 @@
         <v>27</v>
       </c>
       <c r="H166" s="5" t="s">
-        <v>591</v>
+        <v>609</v>
       </c>
     </row>
     <row r="167" ht="42" customHeight="1" spans="1:8">
@@ -26771,7 +26823,7 @@
         <v>254</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>593</v>
+        <v>611</v>
       </c>
       <c r="F167" s="4" t="s">
         <v>26</v>
@@ -26780,7 +26832,7 @@
         <v>27</v>
       </c>
       <c r="H167" s="5" t="s">
-        <v>591</v>
+        <v>609</v>
       </c>
     </row>
     <row r="168" ht="42" customHeight="1" spans="1:8">
@@ -26797,7 +26849,7 @@
         <v>254</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>594</v>
+        <v>612</v>
       </c>
       <c r="F168" s="4" t="s">
         <v>26</v>
@@ -26806,7 +26858,7 @@
         <v>27</v>
       </c>
       <c r="H168" s="5" t="s">
-        <v>591</v>
+        <v>609</v>
       </c>
     </row>
     <row r="169" ht="42" customHeight="1" spans="1:8">
@@ -26823,7 +26875,7 @@
         <v>254</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>595</v>
+        <v>613</v>
       </c>
       <c r="F169" s="4" t="s">
         <v>26</v>
@@ -26832,7 +26884,7 @@
         <v>27</v>
       </c>
       <c r="H169" s="5" t="s">
-        <v>591</v>
+        <v>609</v>
       </c>
     </row>
     <row r="170" ht="42" customHeight="1" spans="1:8">
@@ -26849,7 +26901,7 @@
         <v>254</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>596</v>
+        <v>614</v>
       </c>
       <c r="F170" s="4" t="s">
         <v>26</v>
@@ -26858,7 +26910,7 @@
         <v>27</v>
       </c>
       <c r="H170" s="5" t="s">
-        <v>591</v>
+        <v>609</v>
       </c>
     </row>
     <row r="171" ht="42" customHeight="1" spans="1:8">
@@ -26875,7 +26927,7 @@
         <v>254</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>597</v>
+        <v>615</v>
       </c>
       <c r="F171" s="4" t="s">
         <v>26</v>
@@ -26884,7 +26936,7 @@
         <v>27</v>
       </c>
       <c r="H171" s="5" t="s">
-        <v>591</v>
+        <v>609</v>
       </c>
     </row>
     <row r="172" ht="42" customHeight="1" spans="1:8">
@@ -26906,7 +26958,7 @@
         <v>188</v>
       </c>
       <c r="H172" s="5" t="s">
-        <v>598</v>
+        <v>616</v>
       </c>
     </row>
     <row r="173" ht="42" customHeight="1" spans="1:8">
@@ -26923,7 +26975,7 @@
         <v>261</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>599</v>
+        <v>617</v>
       </c>
       <c r="F173" s="4" t="s">
         <v>26</v>
@@ -26932,7 +26984,7 @@
         <v>27</v>
       </c>
       <c r="H173" s="5" t="s">
-        <v>600</v>
+        <v>618</v>
       </c>
     </row>
     <row r="174" ht="42" customHeight="1" spans="1:8">
@@ -26949,7 +27001,7 @@
         <v>261</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>601</v>
+        <v>619</v>
       </c>
       <c r="F174" s="4" t="s">
         <v>26</v>
@@ -26958,7 +27010,7 @@
         <v>27</v>
       </c>
       <c r="H174" s="5" t="s">
-        <v>600</v>
+        <v>618</v>
       </c>
     </row>
     <row r="175" ht="42" customHeight="1" spans="1:8">
@@ -26975,7 +27027,7 @@
         <v>261</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>602</v>
+        <v>620</v>
       </c>
       <c r="F175" s="4" t="s">
         <v>26</v>
@@ -26984,7 +27036,7 @@
         <v>27</v>
       </c>
       <c r="H175" s="5" t="s">
-        <v>600</v>
+        <v>618</v>
       </c>
     </row>
     <row r="176" ht="42" customHeight="1" spans="1:8">
@@ -27001,7 +27053,7 @@
         <v>261</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>603</v>
+        <v>621</v>
       </c>
       <c r="F176" s="4" t="s">
         <v>26</v>
@@ -27010,7 +27062,7 @@
         <v>27</v>
       </c>
       <c r="H176" s="5" t="s">
-        <v>600</v>
+        <v>618</v>
       </c>
     </row>
     <row r="177" ht="42" customHeight="1" spans="1:8">
@@ -27027,7 +27079,7 @@
         <v>261</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>604</v>
+        <v>622</v>
       </c>
       <c r="F177" s="4" t="s">
         <v>26</v>
@@ -27036,7 +27088,7 @@
         <v>27</v>
       </c>
       <c r="H177" s="5" t="s">
-        <v>600</v>
+        <v>618</v>
       </c>
     </row>
     <row r="178" ht="42" customHeight="1" spans="1:8">
@@ -27058,7 +27110,7 @@
         <v>188</v>
       </c>
       <c r="H178" s="5" t="s">
-        <v>605</v>
+        <v>623</v>
       </c>
     </row>
     <row r="179" ht="42" customHeight="1" spans="1:8">
@@ -27075,7 +27127,7 @@
         <v>269</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>606</v>
+        <v>624</v>
       </c>
       <c r="F179" s="4" t="s">
         <v>26</v>
@@ -27084,7 +27136,7 @@
         <v>27</v>
       </c>
       <c r="H179" s="5" t="s">
-        <v>607</v>
+        <v>625</v>
       </c>
     </row>
     <row r="180" ht="42" customHeight="1" spans="1:8">
@@ -27101,7 +27153,7 @@
         <v>269</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="F180" s="4" t="s">
         <v>26</v>
@@ -27110,7 +27162,7 @@
         <v>27</v>
       </c>
       <c r="H180" s="5" t="s">
-        <v>607</v>
+        <v>625</v>
       </c>
     </row>
     <row r="181" ht="42" customHeight="1" spans="1:8">
@@ -27127,7 +27179,7 @@
         <v>275</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>609</v>
+        <v>627</v>
       </c>
       <c r="F181" s="4" t="s">
         <v>88</v>
@@ -27136,7 +27188,7 @@
         <v>184</v>
       </c>
       <c r="H181" s="5" t="s">
-        <v>610</v>
+        <v>628</v>
       </c>
     </row>
     <row r="182" ht="42" customHeight="1" spans="1:8">
@@ -27153,7 +27205,7 @@
         <v>275</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>611</v>
+        <v>629</v>
       </c>
       <c r="F182" s="4" t="s">
         <v>88</v>
@@ -27162,7 +27214,7 @@
         <v>184</v>
       </c>
       <c r="H182" s="5" t="s">
-        <v>610</v>
+        <v>628</v>
       </c>
     </row>
     <row r="183" ht="42" customHeight="1" spans="1:8">
@@ -27179,7 +27231,7 @@
         <v>275</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>612</v>
+        <v>630</v>
       </c>
       <c r="F183" s="4" t="s">
         <v>88</v>
@@ -27188,7 +27240,7 @@
         <v>184</v>
       </c>
       <c r="H183" s="5" t="s">
-        <v>610</v>
+        <v>628</v>
       </c>
     </row>
     <row r="184" ht="42" customHeight="1" spans="1:8">
@@ -27205,7 +27257,7 @@
         <v>275</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>613</v>
+        <v>631</v>
       </c>
       <c r="F184" s="4" t="s">
         <v>88</v>
@@ -27214,7 +27266,7 @@
         <v>184</v>
       </c>
       <c r="H184" s="5" t="s">
-        <v>610</v>
+        <v>628</v>
       </c>
     </row>
     <row r="185" ht="42" customHeight="1" spans="1:8">
@@ -27231,7 +27283,7 @@
         <v>275</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>614</v>
+        <v>632</v>
       </c>
       <c r="F185" s="4" t="s">
         <v>88</v>
@@ -27240,7 +27292,7 @@
         <v>184</v>
       </c>
       <c r="H185" s="5" t="s">
-        <v>610</v>
+        <v>628</v>
       </c>
     </row>
     <row r="186" ht="42" customHeight="1" spans="1:8">
@@ -27257,7 +27309,7 @@
         <v>281</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>615</v>
+        <v>633</v>
       </c>
       <c r="F186" s="4" t="s">
         <v>26</v>
@@ -27266,7 +27318,7 @@
         <v>27</v>
       </c>
       <c r="H186" s="5" t="s">
-        <v>616</v>
+        <v>634</v>
       </c>
     </row>
     <row r="187" ht="42" customHeight="1" spans="1:8">
@@ -27283,7 +27335,7 @@
         <v>281</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>617</v>
+        <v>635</v>
       </c>
       <c r="F187" s="4" t="s">
         <v>26</v>
@@ -27292,7 +27344,7 @@
         <v>27</v>
       </c>
       <c r="H187" s="5" t="s">
-        <v>616</v>
+        <v>634</v>
       </c>
     </row>
     <row r="188" ht="42" customHeight="1" spans="1:8">
@@ -27309,7 +27361,7 @@
         <v>281</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>618</v>
+        <v>636</v>
       </c>
       <c r="F188" s="4" t="s">
         <v>26</v>
@@ -27318,7 +27370,7 @@
         <v>27</v>
       </c>
       <c r="H188" s="5" t="s">
-        <v>616</v>
+        <v>634</v>
       </c>
     </row>
     <row r="189" ht="42" customHeight="1" spans="1:8">
@@ -27335,7 +27387,7 @@
         <v>281</v>
       </c>
       <c r="E189" s="4" t="s">
-        <v>619</v>
+        <v>637</v>
       </c>
       <c r="F189" s="4" t="s">
         <v>26</v>
@@ -27344,7 +27396,7 @@
         <v>27</v>
       </c>
       <c r="H189" s="5" t="s">
-        <v>616</v>
+        <v>634</v>
       </c>
     </row>
     <row r="190" ht="42" customHeight="1" spans="1:8">
@@ -27361,7 +27413,7 @@
         <v>281</v>
       </c>
       <c r="E190" s="4" t="s">
-        <v>620</v>
+        <v>638</v>
       </c>
       <c r="F190" s="4" t="s">
         <v>26</v>
@@ -27370,7 +27422,7 @@
         <v>27</v>
       </c>
       <c r="H190" s="5" t="s">
-        <v>616</v>
+        <v>634</v>
       </c>
     </row>
     <row r="191" ht="42" customHeight="1" spans="1:8">
@@ -27387,7 +27439,7 @@
         <v>281</v>
       </c>
       <c r="E191" s="4" t="s">
-        <v>621</v>
+        <v>639</v>
       </c>
       <c r="F191" s="4" t="s">
         <v>26</v>
@@ -27396,7 +27448,7 @@
         <v>27</v>
       </c>
       <c r="H191" s="5" t="s">
-        <v>616</v>
+        <v>634</v>
       </c>
     </row>
     <row r="192" ht="42" customHeight="1" spans="1:8">
@@ -27413,7 +27465,7 @@
         <v>281</v>
       </c>
       <c r="E192" s="4" t="s">
-        <v>622</v>
+        <v>640</v>
       </c>
       <c r="F192" s="4" t="s">
         <v>26</v>
@@ -27422,7 +27474,7 @@
         <v>27</v>
       </c>
       <c r="H192" s="5" t="s">
-        <v>616</v>
+        <v>634</v>
       </c>
     </row>
     <row r="193" ht="42" customHeight="1" spans="1:8">
@@ -27439,7 +27491,7 @@
         <v>281</v>
       </c>
       <c r="E193" s="4" t="s">
-        <v>623</v>
+        <v>641</v>
       </c>
       <c r="F193" s="4" t="s">
         <v>26</v>
@@ -27448,7 +27500,7 @@
         <v>27</v>
       </c>
       <c r="H193" s="5" t="s">
-        <v>616</v>
+        <v>634</v>
       </c>
     </row>
     <row r="194" ht="42" customHeight="1" spans="1:8">
@@ -27465,7 +27517,7 @@
         <v>281</v>
       </c>
       <c r="E194" s="4" t="s">
-        <v>624</v>
+        <v>642</v>
       </c>
       <c r="F194" s="4" t="s">
         <v>26</v>
@@ -27474,7 +27526,7 @@
         <v>27</v>
       </c>
       <c r="H194" s="5" t="s">
-        <v>616</v>
+        <v>634</v>
       </c>
     </row>
     <row r="195" ht="42" customHeight="1" spans="1:8">
@@ -27491,7 +27543,7 @@
         <v>281</v>
       </c>
       <c r="E195" s="4" t="s">
-        <v>625</v>
+        <v>643</v>
       </c>
       <c r="F195" s="4" t="s">
         <v>26</v>
@@ -27500,7 +27552,7 @@
         <v>27</v>
       </c>
       <c r="H195" s="5" t="s">
-        <v>616</v>
+        <v>634</v>
       </c>
     </row>
     <row r="196" ht="42" customHeight="1" spans="1:8">
@@ -27517,7 +27569,7 @@
         <v>281</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>626</v>
+        <v>644</v>
       </c>
       <c r="F196" s="4" t="s">
         <v>26</v>
@@ -27526,7 +27578,7 @@
         <v>27</v>
       </c>
       <c r="H196" s="5" t="s">
-        <v>616</v>
+        <v>634</v>
       </c>
     </row>
     <row r="197" ht="42" customHeight="1" spans="1:8">
@@ -27543,7 +27595,7 @@
         <v>286</v>
       </c>
       <c r="E197" s="4" t="s">
-        <v>627</v>
+        <v>645</v>
       </c>
       <c r="F197" s="4" t="s">
         <v>26</v>
@@ -27569,7 +27621,7 @@
         <v>286</v>
       </c>
       <c r="E198" s="4" t="s">
-        <v>628</v>
+        <v>646</v>
       </c>
       <c r="F198" s="4" t="s">
         <v>26</v>
@@ -27595,7 +27647,7 @@
         <v>286</v>
       </c>
       <c r="E199" s="4" t="s">
-        <v>629</v>
+        <v>647</v>
       </c>
       <c r="F199" s="4" t="s">
         <v>26</v>
@@ -27621,7 +27673,7 @@
         <v>286</v>
       </c>
       <c r="E200" s="4" t="s">
-        <v>630</v>
+        <v>648</v>
       </c>
       <c r="F200" s="4" t="s">
         <v>26</v>
@@ -27647,7 +27699,7 @@
         <v>286</v>
       </c>
       <c r="E201" s="4" t="s">
-        <v>631</v>
+        <v>649</v>
       </c>
       <c r="F201" s="4" t="s">
         <v>26</v>
@@ -27673,7 +27725,7 @@
         <v>291</v>
       </c>
       <c r="E202" s="4" t="s">
-        <v>632</v>
+        <v>650</v>
       </c>
       <c r="F202" s="4" t="s">
         <v>26</v>
@@ -27699,7 +27751,7 @@
         <v>291</v>
       </c>
       <c r="E203" s="4" t="s">
-        <v>633</v>
+        <v>651</v>
       </c>
       <c r="F203" s="4" t="s">
         <v>26</v>
@@ -27725,7 +27777,7 @@
         <v>291</v>
       </c>
       <c r="E204" s="4" t="s">
-        <v>634</v>
+        <v>652</v>
       </c>
       <c r="F204" s="4" t="s">
         <v>26</v>
@@ -27751,7 +27803,7 @@
         <v>291</v>
       </c>
       <c r="E205" s="4" t="s">
-        <v>635</v>
+        <v>653</v>
       </c>
       <c r="F205" s="4" t="s">
         <v>26</v>
@@ -27777,7 +27829,7 @@
         <v>296</v>
       </c>
       <c r="E206" s="4" t="s">
-        <v>636</v>
+        <v>654</v>
       </c>
       <c r="F206" s="4" t="s">
         <v>26</v>
@@ -27786,7 +27838,7 @@
         <v>27</v>
       </c>
       <c r="H206" s="5" t="s">
-        <v>637</v>
+        <v>655</v>
       </c>
     </row>
     <row r="207" ht="42" customHeight="1" spans="1:8">
@@ -27803,7 +27855,7 @@
         <v>296</v>
       </c>
       <c r="E207" s="4" t="s">
-        <v>638</v>
+        <v>656</v>
       </c>
       <c r="F207" s="4" t="s">
         <v>26</v>
@@ -27812,7 +27864,7 @@
         <v>27</v>
       </c>
       <c r="H207" s="5" t="s">
-        <v>637</v>
+        <v>655</v>
       </c>
     </row>
     <row r="208" ht="42" customHeight="1" spans="1:8">
@@ -27829,7 +27881,7 @@
         <v>296</v>
       </c>
       <c r="E208" s="4" t="s">
-        <v>639</v>
+        <v>657</v>
       </c>
       <c r="F208" s="4" t="s">
         <v>26</v>
@@ -27838,7 +27890,7 @@
         <v>27</v>
       </c>
       <c r="H208" s="5" t="s">
-        <v>637</v>
+        <v>655</v>
       </c>
     </row>
     <row r="209" ht="42" customHeight="1" spans="1:8">
@@ -27855,7 +27907,7 @@
         <v>296</v>
       </c>
       <c r="E209" s="4" t="s">
-        <v>640</v>
+        <v>658</v>
       </c>
       <c r="F209" s="4" t="s">
         <v>26</v>
@@ -27864,7 +27916,7 @@
         <v>27</v>
       </c>
       <c r="H209" s="5" t="s">
-        <v>637</v>
+        <v>655</v>
       </c>
     </row>
     <row r="210" ht="42" customHeight="1" spans="1:8">
@@ -27881,7 +27933,7 @@
         <v>296</v>
       </c>
       <c r="E210" s="4" t="s">
-        <v>641</v>
+        <v>659</v>
       </c>
       <c r="F210" s="4" t="s">
         <v>26</v>
@@ -27890,7 +27942,7 @@
         <v>27</v>
       </c>
       <c r="H210" s="5" t="s">
-        <v>637</v>
+        <v>655</v>
       </c>
     </row>
     <row r="211" ht="42" customHeight="1" spans="1:8">
@@ -27907,7 +27959,7 @@
         <v>296</v>
       </c>
       <c r="E211" s="4" t="s">
-        <v>642</v>
+        <v>660</v>
       </c>
       <c r="F211" s="4" t="s">
         <v>26</v>
@@ -27916,7 +27968,7 @@
         <v>27</v>
       </c>
       <c r="H211" s="5" t="s">
-        <v>637</v>
+        <v>655</v>
       </c>
     </row>
     <row r="212" ht="42" customHeight="1" spans="1:8">
@@ -27933,7 +27985,7 @@
         <v>302</v>
       </c>
       <c r="E212" s="4" t="s">
-        <v>643</v>
+        <v>661</v>
       </c>
       <c r="F212" s="4" t="s">
         <v>26</v>
@@ -27942,7 +27994,7 @@
         <v>27</v>
       </c>
       <c r="H212" s="5" t="s">
-        <v>644</v>
+        <v>662</v>
       </c>
     </row>
     <row r="213" ht="42" customHeight="1" spans="1:8">
@@ -27959,7 +28011,7 @@
         <v>302</v>
       </c>
       <c r="E213" s="4" t="s">
-        <v>645</v>
+        <v>663</v>
       </c>
       <c r="F213" s="4" t="s">
         <v>26</v>
@@ -27968,7 +28020,7 @@
         <v>27</v>
       </c>
       <c r="H213" s="5" t="s">
-        <v>644</v>
+        <v>662</v>
       </c>
     </row>
     <row r="214" ht="42" customHeight="1" spans="1:8">
@@ -27985,7 +28037,7 @@
         <v>302</v>
       </c>
       <c r="E214" s="4" t="s">
-        <v>646</v>
+        <v>664</v>
       </c>
       <c r="F214" s="4" t="s">
         <v>26</v>
@@ -27994,7 +28046,7 @@
         <v>27</v>
       </c>
       <c r="H214" s="5" t="s">
-        <v>644</v>
+        <v>662</v>
       </c>
     </row>
     <row r="215" ht="42" customHeight="1" spans="1:8">
@@ -28011,7 +28063,7 @@
         <v>302</v>
       </c>
       <c r="E215" s="4" t="s">
-        <v>647</v>
+        <v>665</v>
       </c>
       <c r="F215" s="4" t="s">
         <v>26</v>
@@ -28020,7 +28072,7 @@
         <v>27</v>
       </c>
       <c r="H215" s="5" t="s">
-        <v>644</v>
+        <v>662</v>
       </c>
     </row>
     <row r="216" ht="42" customHeight="1" spans="1:8">
@@ -28037,7 +28089,7 @@
         <v>307</v>
       </c>
       <c r="E216" s="4" t="s">
-        <v>648</v>
+        <v>666</v>
       </c>
       <c r="F216" s="4" t="s">
         <v>26</v>
@@ -28046,7 +28098,7 @@
         <v>27</v>
       </c>
       <c r="H216" s="5" t="s">
-        <v>649</v>
+        <v>667</v>
       </c>
     </row>
     <row r="217" ht="42" customHeight="1" spans="1:8">
@@ -28063,7 +28115,7 @@
         <v>307</v>
       </c>
       <c r="E217" s="4" t="s">
-        <v>650</v>
+        <v>668</v>
       </c>
       <c r="F217" s="4" t="s">
         <v>26</v>
@@ -28072,7 +28124,7 @@
         <v>27</v>
       </c>
       <c r="H217" s="5" t="s">
-        <v>649</v>
+        <v>667</v>
       </c>
     </row>
     <row r="218" ht="42" customHeight="1" spans="1:8">
@@ -28089,7 +28141,7 @@
         <v>307</v>
       </c>
       <c r="E218" s="4" t="s">
-        <v>651</v>
+        <v>669</v>
       </c>
       <c r="F218" s="4" t="s">
         <v>26</v>
@@ -28098,7 +28150,7 @@
         <v>27</v>
       </c>
       <c r="H218" s="5" t="s">
-        <v>649</v>
+        <v>667</v>
       </c>
     </row>
     <row r="219" ht="42" customHeight="1" spans="1:8">
@@ -28112,10 +28164,10 @@
         <v>21</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>652</v>
+        <v>670</v>
       </c>
       <c r="E219" s="4" t="s">
-        <v>653</v>
+        <v>671</v>
       </c>
       <c r="F219" s="4" t="s">
         <v>26</v>
@@ -28124,7 +28176,7 @@
         <v>27</v>
       </c>
       <c r="H219" s="5" t="s">
-        <v>654</v>
+        <v>672</v>
       </c>
     </row>
     <row r="220" ht="42" customHeight="1" spans="1:8">
@@ -28141,7 +28193,7 @@
         <v>286</v>
       </c>
       <c r="E220" s="4" t="s">
-        <v>655</v>
+        <v>673</v>
       </c>
       <c r="F220" s="4" t="s">
         <v>26</v>
@@ -28150,7 +28202,7 @@
         <v>27</v>
       </c>
       <c r="H220" s="5" t="s">
-        <v>654</v>
+        <v>672</v>
       </c>
     </row>
     <row r="221" ht="42" customHeight="1" spans="1:8">
@@ -28164,10 +28216,10 @@
         <v>21</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>652</v>
+        <v>670</v>
       </c>
       <c r="E221" s="4" t="s">
-        <v>656</v>
+        <v>674</v>
       </c>
       <c r="F221" s="4" t="s">
         <v>26</v>
@@ -28176,7 +28228,7 @@
         <v>27</v>
       </c>
       <c r="H221" s="5" t="s">
-        <v>654</v>
+        <v>672</v>
       </c>
     </row>
     <row r="222" ht="42" customHeight="1" spans="1:8">
@@ -28190,10 +28242,10 @@
         <v>21</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>652</v>
+        <v>670</v>
       </c>
       <c r="E222" s="4" t="s">
-        <v>657</v>
+        <v>675</v>
       </c>
       <c r="F222" s="4" t="s">
         <v>26</v>
@@ -28202,7 +28254,7 @@
         <v>27</v>
       </c>
       <c r="H222" s="5" t="s">
-        <v>654</v>
+        <v>672</v>
       </c>
     </row>
     <row r="223" ht="42" customHeight="1" spans="1:8">
@@ -28219,7 +28271,7 @@
         <v>317</v>
       </c>
       <c r="E223" s="4" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="F223" s="4" t="s">
         <v>26</v>
@@ -28228,7 +28280,7 @@
         <v>27</v>
       </c>
       <c r="H223" s="5" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="224" ht="42" customHeight="1" spans="1:8">
@@ -28245,7 +28297,7 @@
         <v>317</v>
       </c>
       <c r="E224" s="4" t="s">
-        <v>660</v>
+        <v>678</v>
       </c>
       <c r="F224" s="4" t="s">
         <v>26</v>
@@ -28254,7 +28306,7 @@
         <v>27</v>
       </c>
       <c r="H224" s="5" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
     </row>
     <row r="225" ht="42" customHeight="1" spans="1:8">
@@ -28271,7 +28323,7 @@
         <v>323</v>
       </c>
       <c r="E225" s="4" t="s">
-        <v>661</v>
+        <v>679</v>
       </c>
       <c r="F225" s="4" t="s">
         <v>26</v>
@@ -28280,7 +28332,7 @@
         <v>27</v>
       </c>
       <c r="H225" s="5" t="s">
-        <v>662</v>
+        <v>680</v>
       </c>
     </row>
     <row r="226" ht="42" customHeight="1" spans="1:8">
@@ -28297,7 +28349,7 @@
         <v>323</v>
       </c>
       <c r="E226" s="4" t="s">
-        <v>663</v>
+        <v>681</v>
       </c>
       <c r="F226" s="4" t="s">
         <v>26</v>
@@ -28306,7 +28358,7 @@
         <v>27</v>
       </c>
       <c r="H226" s="5" t="s">
-        <v>662</v>
+        <v>680</v>
       </c>
     </row>
     <row r="227" ht="42" customHeight="1" spans="1:8">
@@ -28323,7 +28375,7 @@
         <v>323</v>
       </c>
       <c r="E227" s="4" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="F227" s="4" t="s">
         <v>26</v>
@@ -28332,7 +28384,7 @@
         <v>27</v>
       </c>
       <c r="H227" s="5" t="s">
-        <v>662</v>
+        <v>680</v>
       </c>
     </row>
     <row r="228" ht="42" customHeight="1" spans="1:8">
@@ -28349,7 +28401,7 @@
         <v>323</v>
       </c>
       <c r="E228" s="4" t="s">
-        <v>664</v>
+        <v>682</v>
       </c>
       <c r="F228" s="4" t="s">
         <v>26</v>
@@ -28358,7 +28410,7 @@
         <v>27</v>
       </c>
       <c r="H228" s="5" t="s">
-        <v>662</v>
+        <v>680</v>
       </c>
     </row>
     <row r="229" ht="42" customHeight="1" spans="1:8">
@@ -28375,7 +28427,7 @@
         <v>211</v>
       </c>
       <c r="E229" s="4" t="s">
-        <v>665</v>
+        <v>683</v>
       </c>
       <c r="F229" s="4" t="s">
         <v>26</v>
@@ -28384,7 +28436,7 @@
         <v>27</v>
       </c>
       <c r="H229" s="5" t="s">
-        <v>666</v>
+        <v>684</v>
       </c>
     </row>
     <row r="230" ht="42" customHeight="1" spans="1:8">
@@ -28398,10 +28450,10 @@
         <v>21</v>
       </c>
       <c r="D230" s="4" t="s">
-        <v>667</v>
+        <v>685</v>
       </c>
       <c r="E230" s="4" t="s">
-        <v>668</v>
+        <v>686</v>
       </c>
       <c r="F230" s="4" t="s">
         <v>26</v>
@@ -28410,7 +28462,7 @@
         <v>27</v>
       </c>
       <c r="H230" s="5" t="s">
-        <v>666</v>
+        <v>684</v>
       </c>
     </row>
     <row r="231" ht="42" customHeight="1" spans="1:8">
@@ -28427,7 +28479,7 @@
         <v>211</v>
       </c>
       <c r="E231" s="4" t="s">
-        <v>669</v>
+        <v>687</v>
       </c>
       <c r="F231" s="4" t="s">
         <v>26</v>
@@ -28436,7 +28488,7 @@
         <v>27</v>
       </c>
       <c r="H231" s="5" t="s">
-        <v>666</v>
+        <v>684</v>
       </c>
     </row>
     <row r="232" ht="42" customHeight="1" spans="1:8">
@@ -28450,10 +28502,10 @@
         <v>21</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>667</v>
+        <v>685</v>
       </c>
       <c r="E232" s="4" t="s">
-        <v>670</v>
+        <v>688</v>
       </c>
       <c r="F232" s="4" t="s">
         <v>26</v>
@@ -28462,7 +28514,7 @@
         <v>27</v>
       </c>
       <c r="H232" s="5" t="s">
-        <v>666</v>
+        <v>684</v>
       </c>
     </row>
     <row r="233" ht="42" customHeight="1" spans="1:8">
@@ -28479,7 +28531,7 @@
         <v>211</v>
       </c>
       <c r="E233" s="4" t="s">
-        <v>502</v>
+        <v>520</v>
       </c>
       <c r="F233" s="4" t="s">
         <v>26</v>
@@ -28488,7 +28540,7 @@
         <v>27</v>
       </c>
       <c r="H233" s="5" t="s">
-        <v>666</v>
+        <v>684</v>
       </c>
     </row>
     <row r="234" ht="42" customHeight="1" spans="1:8">
@@ -28505,7 +28557,7 @@
         <v>211</v>
       </c>
       <c r="E234" s="4" t="s">
-        <v>671</v>
+        <v>689</v>
       </c>
       <c r="F234" s="4" t="s">
         <v>26</v>
@@ -28514,7 +28566,7 @@
         <v>27</v>
       </c>
       <c r="H234" s="5" t="s">
-        <v>666</v>
+        <v>684</v>
       </c>
     </row>
     <row r="235" ht="42" customHeight="1" spans="1:8">
@@ -28528,10 +28580,10 @@
         <v>21</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>667</v>
+        <v>685</v>
       </c>
       <c r="E235" s="4" t="s">
-        <v>672</v>
+        <v>690</v>
       </c>
       <c r="F235" s="4" t="s">
         <v>26</v>
@@ -28540,7 +28592,7 @@
         <v>27</v>
       </c>
       <c r="H235" s="5" t="s">
-        <v>666</v>
+        <v>684</v>
       </c>
     </row>
     <row r="236" ht="42" customHeight="1" spans="1:8">
@@ -28554,10 +28606,10 @@
         <v>21</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>667</v>
+        <v>685</v>
       </c>
       <c r="E236" s="4" t="s">
-        <v>673</v>
+        <v>691</v>
       </c>
       <c r="F236" s="4" t="s">
         <v>26</v>
@@ -28566,7 +28618,7 @@
         <v>27</v>
       </c>
       <c r="H236" s="5" t="s">
-        <v>666</v>
+        <v>684</v>
       </c>
     </row>
     <row r="237" ht="42" customHeight="1" spans="1:8">
@@ -28583,7 +28635,7 @@
         <v>334</v>
       </c>
       <c r="E237" s="4" t="s">
-        <v>674</v>
+        <v>692</v>
       </c>
       <c r="F237" s="4" t="s">
         <v>26</v>
@@ -28592,7 +28644,7 @@
         <v>27</v>
       </c>
       <c r="H237" s="5" t="s">
-        <v>675</v>
+        <v>693</v>
       </c>
     </row>
     <row r="238" ht="42" customHeight="1" spans="1:8">
@@ -28609,7 +28661,7 @@
         <v>334</v>
       </c>
       <c r="E238" s="4" t="s">
-        <v>676</v>
+        <v>694</v>
       </c>
       <c r="F238" s="4" t="s">
         <v>26</v>
@@ -28618,7 +28670,7 @@
         <v>27</v>
       </c>
       <c r="H238" s="5" t="s">
-        <v>675</v>
+        <v>693</v>
       </c>
     </row>
     <row r="239" ht="42" customHeight="1" spans="1:8">
@@ -28635,7 +28687,7 @@
         <v>334</v>
       </c>
       <c r="E239" s="4" t="s">
-        <v>677</v>
+        <v>695</v>
       </c>
       <c r="F239" s="4" t="s">
         <v>26</v>
@@ -28644,7 +28696,7 @@
         <v>27</v>
       </c>
       <c r="H239" s="5" t="s">
-        <v>675</v>
+        <v>693</v>
       </c>
     </row>
     <row r="240" ht="42" customHeight="1" spans="1:8">
@@ -28661,7 +28713,7 @@
         <v>334</v>
       </c>
       <c r="E240" s="4" t="s">
-        <v>678</v>
+        <v>696</v>
       </c>
       <c r="F240" s="4" t="s">
         <v>26</v>
@@ -28670,7 +28722,7 @@
         <v>27</v>
       </c>
       <c r="H240" s="5" t="s">
-        <v>675</v>
+        <v>693</v>
       </c>
     </row>
     <row r="241" ht="42" customHeight="1" spans="1:8">
@@ -28687,7 +28739,7 @@
         <v>334</v>
       </c>
       <c r="E241" s="4" t="s">
-        <v>679</v>
+        <v>697</v>
       </c>
       <c r="F241" s="4" t="s">
         <v>26</v>
@@ -28696,7 +28748,7 @@
         <v>27</v>
       </c>
       <c r="H241" s="5" t="s">
-        <v>675</v>
+        <v>693</v>
       </c>
     </row>
     <row r="242" ht="42" customHeight="1" spans="1:8">
@@ -28713,7 +28765,7 @@
         <v>334</v>
       </c>
       <c r="E242" s="4" t="s">
-        <v>680</v>
+        <v>698</v>
       </c>
       <c r="F242" s="4" t="s">
         <v>26</v>
@@ -28722,7 +28774,7 @@
         <v>27</v>
       </c>
       <c r="H242" s="5" t="s">
-        <v>675</v>
+        <v>693</v>
       </c>
     </row>
     <row r="243" ht="42" customHeight="1" spans="1:8">
@@ -28739,7 +28791,7 @@
         <v>340</v>
       </c>
       <c r="E243" s="4" t="s">
-        <v>681</v>
+        <v>699</v>
       </c>
       <c r="F243" s="4" t="s">
         <v>26</v>
@@ -28748,7 +28800,7 @@
         <v>27</v>
       </c>
       <c r="H243" s="5" t="s">
-        <v>682</v>
+        <v>700</v>
       </c>
     </row>
     <row r="244" ht="42" customHeight="1" spans="1:8">
@@ -28765,7 +28817,7 @@
         <v>340</v>
       </c>
       <c r="E244" s="4" t="s">
-        <v>683</v>
+        <v>701</v>
       </c>
       <c r="F244" s="4" t="s">
         <v>26</v>
@@ -28774,7 +28826,7 @@
         <v>27</v>
       </c>
       <c r="H244" s="5" t="s">
-        <v>682</v>
+        <v>700</v>
       </c>
     </row>
     <row r="245" ht="42" customHeight="1" spans="1:8">
@@ -28791,7 +28843,7 @@
         <v>340</v>
       </c>
       <c r="E245" s="4" t="s">
-        <v>684</v>
+        <v>702</v>
       </c>
       <c r="F245" s="4" t="s">
         <v>26</v>
@@ -28800,7 +28852,7 @@
         <v>27</v>
       </c>
       <c r="H245" s="5" t="s">
-        <v>682</v>
+        <v>700</v>
       </c>
     </row>
     <row r="246" ht="42" customHeight="1" spans="1:8">
@@ -28817,7 +28869,7 @@
         <v>340</v>
       </c>
       <c r="E246" s="4" t="s">
-        <v>685</v>
+        <v>703</v>
       </c>
       <c r="F246" s="4" t="s">
         <v>26</v>
@@ -28826,7 +28878,7 @@
         <v>27</v>
       </c>
       <c r="H246" s="5" t="s">
-        <v>682</v>
+        <v>700</v>
       </c>
     </row>
     <row r="247" ht="42" customHeight="1" spans="1:8">
@@ -28843,7 +28895,7 @@
         <v>340</v>
       </c>
       <c r="E247" s="4" t="s">
-        <v>686</v>
+        <v>704</v>
       </c>
       <c r="F247" s="4" t="s">
         <v>26</v>
@@ -28852,7 +28904,7 @@
         <v>27</v>
       </c>
       <c r="H247" s="5" t="s">
-        <v>682</v>
+        <v>700</v>
       </c>
     </row>
     <row r="248" ht="42" customHeight="1" spans="1:8">
@@ -28869,7 +28921,7 @@
         <v>340</v>
       </c>
       <c r="E248" s="4" t="s">
-        <v>687</v>
+        <v>705</v>
       </c>
       <c r="F248" s="4" t="s">
         <v>26</v>
@@ -28878,7 +28930,7 @@
         <v>27</v>
       </c>
       <c r="H248" s="5" t="s">
-        <v>682</v>
+        <v>700</v>
       </c>
     </row>
     <row r="249" ht="42" customHeight="1" spans="1:8">
@@ -28895,7 +28947,7 @@
         <v>340</v>
       </c>
       <c r="E249" s="4" t="s">
-        <v>688</v>
+        <v>706</v>
       </c>
       <c r="F249" s="4" t="s">
         <v>26</v>
@@ -28904,7 +28956,7 @@
         <v>27</v>
       </c>
       <c r="H249" s="5" t="s">
-        <v>682</v>
+        <v>700</v>
       </c>
     </row>
     <row r="250" ht="42" customHeight="1" spans="1:8">
@@ -28921,7 +28973,7 @@
         <v>345</v>
       </c>
       <c r="E250" s="4" t="s">
-        <v>689</v>
+        <v>707</v>
       </c>
       <c r="F250" s="4" t="s">
         <v>26</v>
@@ -28930,7 +28982,7 @@
         <v>27</v>
       </c>
       <c r="H250" s="5" t="s">
-        <v>690</v>
+        <v>708</v>
       </c>
     </row>
     <row r="251" ht="42" customHeight="1" spans="1:8">
@@ -28947,7 +28999,7 @@
         <v>345</v>
       </c>
       <c r="E251" s="4" t="s">
-        <v>691</v>
+        <v>709</v>
       </c>
       <c r="F251" s="4" t="s">
         <v>26</v>
@@ -28956,7 +29008,7 @@
         <v>27</v>
       </c>
       <c r="H251" s="5" t="s">
-        <v>690</v>
+        <v>708</v>
       </c>
     </row>
     <row r="252" ht="42" customHeight="1" spans="1:8">
@@ -28973,7 +29025,7 @@
         <v>345</v>
       </c>
       <c r="E252" s="4" t="s">
-        <v>692</v>
+        <v>710</v>
       </c>
       <c r="F252" s="4" t="s">
         <v>26</v>
@@ -28982,7 +29034,7 @@
         <v>27</v>
       </c>
       <c r="H252" s="5" t="s">
-        <v>690</v>
+        <v>708</v>
       </c>
     </row>
     <row r="253" ht="42" customHeight="1" spans="1:8">
@@ -28999,7 +29051,7 @@
         <v>345</v>
       </c>
       <c r="E253" s="4" t="s">
-        <v>693</v>
+        <v>711</v>
       </c>
       <c r="F253" s="4" t="s">
         <v>26</v>
@@ -29008,7 +29060,7 @@
         <v>27</v>
       </c>
       <c r="H253" s="5" t="s">
-        <v>690</v>
+        <v>708</v>
       </c>
     </row>
     <row r="254" ht="42" customHeight="1" spans="1:8">
@@ -29025,7 +29077,7 @@
         <v>345</v>
       </c>
       <c r="E254" s="4" t="s">
-        <v>694</v>
+        <v>712</v>
       </c>
       <c r="F254" s="4" t="s">
         <v>26</v>
@@ -29034,7 +29086,7 @@
         <v>27</v>
       </c>
       <c r="H254" s="5" t="s">
-        <v>690</v>
+        <v>708</v>
       </c>
     </row>
     <row r="255" ht="42" customHeight="1" spans="1:8">
@@ -29051,7 +29103,7 @@
         <v>350</v>
       </c>
       <c r="E255" s="4" t="s">
-        <v>695</v>
+        <v>713</v>
       </c>
       <c r="F255" s="4" t="s">
         <v>26</v>
@@ -29060,7 +29112,7 @@
         <v>27</v>
       </c>
       <c r="H255" s="5" t="s">
-        <v>696</v>
+        <v>714</v>
       </c>
     </row>
     <row r="256" ht="42" customHeight="1" spans="1:8">
@@ -29077,7 +29129,7 @@
         <v>350</v>
       </c>
       <c r="E256" s="4" t="s">
-        <v>697</v>
+        <v>715</v>
       </c>
       <c r="F256" s="4" t="s">
         <v>26</v>
@@ -29086,7 +29138,7 @@
         <v>27</v>
       </c>
       <c r="H256" s="5" t="s">
-        <v>696</v>
+        <v>714</v>
       </c>
     </row>
     <row r="257" ht="42" customHeight="1" spans="1:8">
@@ -29103,7 +29155,7 @@
         <v>350</v>
       </c>
       <c r="E257" s="4" t="s">
-        <v>698</v>
+        <v>716</v>
       </c>
       <c r="F257" s="4" t="s">
         <v>26</v>
@@ -29112,7 +29164,7 @@
         <v>27</v>
       </c>
       <c r="H257" s="5" t="s">
-        <v>696</v>
+        <v>714</v>
       </c>
     </row>
     <row r="258" ht="42" customHeight="1" spans="1:8">
@@ -29151,7 +29203,7 @@
         <v>357</v>
       </c>
       <c r="E259" s="4" t="s">
-        <v>699</v>
+        <v>717</v>
       </c>
       <c r="F259" s="4" t="s">
         <v>26</v>
@@ -29160,7 +29212,7 @@
         <v>27</v>
       </c>
       <c r="H259" s="5" t="s">
-        <v>700</v>
+        <v>718</v>
       </c>
     </row>
     <row r="260" ht="42" customHeight="1" spans="1:8">
@@ -29177,7 +29229,7 @@
         <v>357</v>
       </c>
       <c r="E260" s="4" t="s">
-        <v>701</v>
+        <v>719</v>
       </c>
       <c r="F260" s="4" t="s">
         <v>26</v>
@@ -29186,7 +29238,7 @@
         <v>27</v>
       </c>
       <c r="H260" s="5" t="s">
-        <v>700</v>
+        <v>718</v>
       </c>
     </row>
     <row r="261" ht="42" customHeight="1" spans="1:8">
@@ -29203,7 +29255,7 @@
         <v>357</v>
       </c>
       <c r="E261" s="4" t="s">
-        <v>702</v>
+        <v>720</v>
       </c>
       <c r="F261" s="4" t="s">
         <v>26</v>
@@ -29212,7 +29264,7 @@
         <v>27</v>
       </c>
       <c r="H261" s="5" t="s">
-        <v>700</v>
+        <v>718</v>
       </c>
     </row>
     <row r="262" ht="42" customHeight="1" spans="1:8">
@@ -29229,7 +29281,7 @@
         <v>357</v>
       </c>
       <c r="E262" s="4" t="s">
-        <v>703</v>
+        <v>721</v>
       </c>
       <c r="F262" s="4" t="s">
         <v>26</v>
@@ -29238,7 +29290,7 @@
         <v>27</v>
       </c>
       <c r="H262" s="5" t="s">
-        <v>700</v>
+        <v>718</v>
       </c>
     </row>
     <row r="263" ht="42" customHeight="1" spans="1:8">
@@ -29255,7 +29307,7 @@
         <v>357</v>
       </c>
       <c r="E263" s="4" t="s">
-        <v>704</v>
+        <v>722</v>
       </c>
       <c r="F263" s="4" t="s">
         <v>26</v>
@@ -29264,7 +29316,7 @@
         <v>27</v>
       </c>
       <c r="H263" s="5" t="s">
-        <v>700</v>
+        <v>718</v>
       </c>
     </row>
     <row r="264" ht="42" customHeight="1" spans="1:8">
@@ -29281,7 +29333,7 @@
         <v>357</v>
       </c>
       <c r="E264" s="4" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="F264" s="4" t="s">
         <v>26</v>
@@ -29290,7 +29342,7 @@
         <v>27</v>
       </c>
       <c r="H264" s="5" t="s">
-        <v>700</v>
+        <v>718</v>
       </c>
     </row>
     <row r="265" ht="42" customHeight="1" spans="1:8">
@@ -29307,7 +29359,7 @@
         <v>362</v>
       </c>
       <c r="E265" s="4" t="s">
-        <v>705</v>
+        <v>723</v>
       </c>
       <c r="F265" s="4" t="s">
         <v>26</v>
@@ -29316,7 +29368,7 @@
         <v>27</v>
       </c>
       <c r="H265" s="5" t="s">
-        <v>706</v>
+        <v>724</v>
       </c>
     </row>
     <row r="266" ht="42" customHeight="1" spans="1:8">
@@ -29333,7 +29385,7 @@
         <v>362</v>
       </c>
       <c r="E266" s="4" t="s">
-        <v>707</v>
+        <v>725</v>
       </c>
       <c r="F266" s="4" t="s">
         <v>26</v>
@@ -29342,7 +29394,7 @@
         <v>27</v>
       </c>
       <c r="H266" s="5" t="s">
-        <v>706</v>
+        <v>724</v>
       </c>
     </row>
     <row r="267" ht="42" customHeight="1" spans="1:8">
@@ -29359,7 +29411,7 @@
         <v>366</v>
       </c>
       <c r="E267" s="4" t="s">
-        <v>708</v>
+        <v>726</v>
       </c>
       <c r="F267" s="4" t="s">
         <v>26</v>
@@ -29368,7 +29420,7 @@
         <v>27</v>
       </c>
       <c r="H267" s="5" t="s">
-        <v>709</v>
+        <v>727</v>
       </c>
     </row>
     <row r="268" ht="42" customHeight="1" spans="1:8">
@@ -29385,7 +29437,7 @@
         <v>366</v>
       </c>
       <c r="E268" s="4" t="s">
-        <v>710</v>
+        <v>728</v>
       </c>
       <c r="F268" s="4" t="s">
         <v>26</v>
@@ -29394,7 +29446,7 @@
         <v>27</v>
       </c>
       <c r="H268" s="5" t="s">
-        <v>709</v>
+        <v>727</v>
       </c>
     </row>
     <row r="269" ht="42" customHeight="1" spans="1:8">
@@ -29411,7 +29463,7 @@
         <v>371</v>
       </c>
       <c r="E269" s="4" t="s">
-        <v>711</v>
+        <v>729</v>
       </c>
       <c r="F269" s="4" t="s">
         <v>26</v>
@@ -29420,7 +29472,7 @@
         <v>27</v>
       </c>
       <c r="H269" s="5" t="s">
-        <v>712</v>
+        <v>730</v>
       </c>
     </row>
     <row r="270" ht="42" customHeight="1" spans="1:8">
@@ -29437,7 +29489,7 @@
         <v>371</v>
       </c>
       <c r="E270" s="4" t="s">
-        <v>713</v>
+        <v>731</v>
       </c>
       <c r="F270" s="4" t="s">
         <v>26</v>
@@ -29446,7 +29498,7 @@
         <v>27</v>
       </c>
       <c r="H270" s="5" t="s">
-        <v>712</v>
+        <v>730</v>
       </c>
     </row>
     <row r="271" ht="42" customHeight="1" spans="1:8">
@@ -29463,7 +29515,7 @@
         <v>371</v>
       </c>
       <c r="E271" s="4" t="s">
-        <v>714</v>
+        <v>732</v>
       </c>
       <c r="F271" s="4" t="s">
         <v>26</v>
@@ -29472,7 +29524,7 @@
         <v>27</v>
       </c>
       <c r="H271" s="5" t="s">
-        <v>712</v>
+        <v>730</v>
       </c>
     </row>
     <row r="272" ht="42" customHeight="1" spans="1:8">
@@ -29489,7 +29541,7 @@
         <v>371</v>
       </c>
       <c r="E272" s="4" t="s">
-        <v>715</v>
+        <v>733</v>
       </c>
       <c r="F272" s="4" t="s">
         <v>26</v>
@@ -29498,7 +29550,7 @@
         <v>27</v>
       </c>
       <c r="H272" s="5" t="s">
-        <v>712</v>
+        <v>730</v>
       </c>
     </row>
     <row r="273" ht="42" customHeight="1" spans="1:8">
@@ -29515,7 +29567,7 @@
         <v>371</v>
       </c>
       <c r="E273" s="4" t="s">
-        <v>716</v>
+        <v>734</v>
       </c>
       <c r="F273" s="4" t="s">
         <v>26</v>
@@ -29524,7 +29576,7 @@
         <v>27</v>
       </c>
       <c r="H273" s="5" t="s">
-        <v>712</v>
+        <v>730</v>
       </c>
     </row>
     <row r="274" ht="42" customHeight="1" spans="1:8">
@@ -29563,7 +29615,7 @@
         <v>378</v>
       </c>
       <c r="E275" s="4" t="s">
-        <v>717</v>
+        <v>735</v>
       </c>
       <c r="F275" s="4" t="s">
         <v>26</v>
@@ -29572,7 +29624,7 @@
         <v>27</v>
       </c>
       <c r="H275" s="5" t="s">
-        <v>718</v>
+        <v>736</v>
       </c>
     </row>
     <row r="276" ht="42" customHeight="1" spans="1:8">
@@ -29589,7 +29641,7 @@
         <v>378</v>
       </c>
       <c r="E276" s="4" t="s">
-        <v>719</v>
+        <v>737</v>
       </c>
       <c r="F276" s="4" t="s">
         <v>26</v>
@@ -29598,7 +29650,7 @@
         <v>27</v>
       </c>
       <c r="H276" s="5" t="s">
-        <v>718</v>
+        <v>736</v>
       </c>
     </row>
     <row r="277" ht="42" customHeight="1" spans="1:8">
@@ -29615,7 +29667,7 @@
         <v>378</v>
       </c>
       <c r="E277" s="4" t="s">
-        <v>720</v>
+        <v>738</v>
       </c>
       <c r="F277" s="4" t="s">
         <v>26</v>
@@ -29624,7 +29676,7 @@
         <v>27</v>
       </c>
       <c r="H277" s="5" t="s">
-        <v>718</v>
+        <v>736</v>
       </c>
     </row>
     <row r="278" ht="42" customHeight="1" spans="1:8">
@@ -29641,7 +29693,7 @@
         <v>383</v>
       </c>
       <c r="E278" s="4" t="s">
-        <v>721</v>
+        <v>739</v>
       </c>
       <c r="F278" s="4" t="s">
         <v>26</v>
@@ -29650,7 +29702,7 @@
         <v>27</v>
       </c>
       <c r="H278" s="5" t="s">
-        <v>722</v>
+        <v>740</v>
       </c>
     </row>
     <row r="279" ht="42" customHeight="1" spans="1:8">
@@ -29667,7 +29719,7 @@
         <v>383</v>
       </c>
       <c r="E279" s="4" t="s">
-        <v>723</v>
+        <v>741</v>
       </c>
       <c r="F279" s="4" t="s">
         <v>26</v>
@@ -29676,7 +29728,7 @@
         <v>27</v>
       </c>
       <c r="H279" s="5" t="s">
-        <v>722</v>
+        <v>740</v>
       </c>
     </row>
     <row r="280" ht="42" customHeight="1" spans="1:8">
@@ -29693,7 +29745,7 @@
         <v>388</v>
       </c>
       <c r="E280" s="4" t="s">
-        <v>724</v>
+        <v>742</v>
       </c>
       <c r="F280" s="4" t="s">
         <v>26</v>
@@ -29702,7 +29754,7 @@
         <v>27</v>
       </c>
       <c r="H280" s="5" t="s">
-        <v>725</v>
+        <v>743</v>
       </c>
     </row>
     <row r="281" ht="42" customHeight="1" spans="1:8">
@@ -29719,7 +29771,7 @@
         <v>388</v>
       </c>
       <c r="E281" s="4" t="s">
-        <v>726</v>
+        <v>744</v>
       </c>
       <c r="F281" s="4" t="s">
         <v>26</v>
@@ -29728,7 +29780,7 @@
         <v>27</v>
       </c>
       <c r="H281" s="5" t="s">
-        <v>725</v>
+        <v>743</v>
       </c>
     </row>
     <row r="282" ht="42" customHeight="1" spans="1:8">
@@ -29745,7 +29797,7 @@
         <v>388</v>
       </c>
       <c r="E282" s="4" t="s">
-        <v>727</v>
+        <v>745</v>
       </c>
       <c r="F282" s="4" t="s">
         <v>26</v>
@@ -29754,7 +29806,7 @@
         <v>27</v>
       </c>
       <c r="H282" s="5" t="s">
-        <v>725</v>
+        <v>743</v>
       </c>
     </row>
     <row r="283" ht="42" customHeight="1" spans="1:8">
@@ -29777,7 +29829,7 @@
         <v>394</v>
       </c>
       <c r="G283" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H283" s="8" t="s">
         <v>393</v>
@@ -29788,7 +29840,7 @@
         <v>390</v>
       </c>
       <c r="B284" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C284" s="6" t="s">
         <v>392</v>
@@ -29803,10 +29855,10 @@
         <v>394</v>
       </c>
       <c r="G284" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H284" s="8" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="285" ht="42" customHeight="1" spans="1:8">
@@ -29814,7 +29866,7 @@
         <v>390</v>
       </c>
       <c r="B285" s="6" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C285" s="6" t="s">
         <v>392</v>
@@ -29829,10 +29881,10 @@
         <v>394</v>
       </c>
       <c r="G285" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H285" s="8" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="286" ht="42" customHeight="1" spans="1:8">
@@ -29840,7 +29892,7 @@
         <v>390</v>
       </c>
       <c r="B286" s="6" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C286" s="6" t="s">
         <v>392</v>
@@ -29855,10 +29907,10 @@
         <v>394</v>
       </c>
       <c r="G286" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H286" s="8" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="287" ht="42" customHeight="1" spans="1:8">
@@ -29866,7 +29918,7 @@
         <v>390</v>
       </c>
       <c r="B287" s="6" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="C287" s="6" t="s">
         <v>392</v>
@@ -29881,10 +29933,10 @@
         <v>394</v>
       </c>
       <c r="G287" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H287" s="8" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="288" ht="42" customHeight="1" spans="1:8">
@@ -29892,7 +29944,7 @@
         <v>390</v>
       </c>
       <c r="B288" s="6" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="C288" s="6" t="s">
         <v>392</v>
@@ -29907,10 +29959,10 @@
         <v>394</v>
       </c>
       <c r="G288" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H288" s="8" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
     </row>
     <row r="289" ht="42" customHeight="1" spans="1:8">
@@ -29918,7 +29970,7 @@
         <v>390</v>
       </c>
       <c r="B289" s="6" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="C289" s="6" t="s">
         <v>392</v>
@@ -29933,10 +29985,10 @@
         <v>394</v>
       </c>
       <c r="G289" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H289" s="8" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="290" ht="42" customHeight="1" spans="1:8">
@@ -29944,7 +29996,7 @@
         <v>390</v>
       </c>
       <c r="B290" s="6" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="C290" s="6" t="s">
         <v>392</v>
@@ -29959,10 +30011,10 @@
         <v>394</v>
       </c>
       <c r="G290" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H290" s="8" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
     </row>
     <row r="291" ht="42" customHeight="1" spans="1:8">
@@ -29970,7 +30022,7 @@
         <v>390</v>
       </c>
       <c r="B291" s="6" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="C291" s="6" t="s">
         <v>392</v>
@@ -29985,10 +30037,10 @@
         <v>394</v>
       </c>
       <c r="G291" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H291" s="8" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
     </row>
     <row r="292" ht="42" customHeight="1" spans="1:8">
@@ -29996,7 +30048,7 @@
         <v>390</v>
       </c>
       <c r="B292" s="6" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C292" s="6" t="s">
         <v>392</v>
@@ -30011,10 +30063,10 @@
         <v>394</v>
       </c>
       <c r="G292" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H292" s="8" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
     </row>
     <row r="293" ht="42" customHeight="1" spans="1:8">
@@ -30022,7 +30074,7 @@
         <v>390</v>
       </c>
       <c r="B293" s="6" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="C293" s="6" t="s">
         <v>392</v>
@@ -30037,10 +30089,10 @@
         <v>394</v>
       </c>
       <c r="G293" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H293" s="8" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
     </row>
     <row r="294" ht="42" customHeight="1" spans="1:8">
@@ -30048,7 +30100,7 @@
         <v>390</v>
       </c>
       <c r="B294" s="6" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="C294" s="6" t="s">
         <v>392</v>
@@ -30063,10 +30115,10 @@
         <v>394</v>
       </c>
       <c r="G294" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H294" s="8" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
     </row>
     <row r="295" ht="42" customHeight="1" spans="1:8">
@@ -30074,7 +30126,7 @@
         <v>390</v>
       </c>
       <c r="B295" s="6" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="C295" s="6" t="s">
         <v>392</v>
@@ -30089,10 +30141,10 @@
         <v>394</v>
       </c>
       <c r="G295" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H295" s="8" t="s">
-        <v>419</v>
+        <v>435</v>
       </c>
     </row>
     <row r="296" ht="42" customHeight="1" spans="1:8">
@@ -30100,7 +30152,7 @@
         <v>390</v>
       </c>
       <c r="B296" s="6" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="C296" s="6" t="s">
         <v>392</v>
@@ -30115,10 +30167,10 @@
         <v>394</v>
       </c>
       <c r="G296" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H296" s="8" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>
